--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G5">

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G5">

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="Q5">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -644,40 +644,40 @@
         <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC2">
         <v>1.8</v>
@@ -686,13 +686,13 @@
         <v>2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>1.44</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>2.76</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU7"/>
+  <dimension ref="A1:AU14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.79</v>
+        <v>2.92</v>
       </c>
       <c r="O2">
-        <v>4.55</v>
+        <v>3.28</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q2">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="R2">
-        <v>2.54</v>
+        <v>2.03</v>
       </c>
       <c r="S2">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>4.35</v>
+        <v>2.88</v>
       </c>
       <c r="U2">
-        <v>1.9</v>
+        <v>2.89</v>
       </c>
       <c r="V2">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2">
+        <v>1.3</v>
+      </c>
+      <c r="Z2">
+        <v>3.15</v>
+      </c>
+      <c r="AA2">
+        <v>1.96</v>
+      </c>
+      <c r="AB2">
+        <v>1.79</v>
+      </c>
+      <c r="AC2">
+        <v>3.44</v>
+      </c>
+      <c r="AD2">
+        <v>1.23</v>
+      </c>
+      <c r="AE2">
         <v>1.04</v>
       </c>
-      <c r="Z2">
-        <v>6.95</v>
-      </c>
-      <c r="AA2">
-        <v>1.33</v>
-      </c>
-      <c r="AB2">
-        <v>3.08</v>
-      </c>
-      <c r="AC2">
-        <v>1.8</v>
-      </c>
-      <c r="AD2">
-        <v>2</v>
-      </c>
-      <c r="AE2">
-        <v>1.35</v>
-      </c>
       <c r="AF2">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="AG2">
-        <v>2.94</v>
+        <v>1.96</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>2.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK2">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-08-04 15:30:00</t>
+          <t>2026-08-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:00:00</t>
+          <t>2026-08-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -914,27 +914,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>5.78</v>
+        <v>1.81</v>
       </c>
       <c r="O4">
-        <v>4.85</v>
+        <v>3.64</v>
       </c>
       <c r="P4">
-        <v>1.44</v>
+        <v>4.2</v>
       </c>
       <c r="Q4">
-        <v>4.78</v>
+        <v>2.33</v>
       </c>
       <c r="R4">
-        <v>2.53</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>1.73</v>
+        <v>2.88</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>7.4</v>
+        <v>2.99</v>
       </c>
       <c r="AA4">
+        <v>2.03</v>
+      </c>
+      <c r="AB4">
+        <v>1.76</v>
+      </c>
+      <c r="AC4">
+        <v>3.38</v>
+      </c>
+      <c r="AD4">
         <v>1.24</v>
       </c>
-      <c r="AB4">
-        <v>3.4</v>
-      </c>
-      <c r="AC4">
-        <v>1.71</v>
-      </c>
-      <c r="AD4">
-        <v>2</v>
-      </c>
       <c r="AE4">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>2.88</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.14</v>
+        <v>1.87</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-08-04 16:15:00</t>
+          <t>2026-08-04 14:30:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>2.76</v>
+        <v>2.25</v>
       </c>
       <c r="Q5">
-        <v>2.82</v>
+        <v>3.74</v>
       </c>
       <c r="R5">
-        <v>2.57</v>
+        <v>2.17</v>
       </c>
       <c r="S5">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="T5">
-        <v>4.45</v>
+        <v>2.81</v>
       </c>
       <c r="U5">
-        <v>1.71</v>
+        <v>2.81</v>
       </c>
       <c r="V5">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>7.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA5">
-        <v>1.28</v>
+        <v>2.02</v>
       </c>
       <c r="AB5">
-        <v>3.34</v>
+        <v>1.83</v>
       </c>
       <c r="AC5">
-        <v>1.64</v>
+        <v>3.3</v>
       </c>
       <c r="AD5">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="AG5">
-        <v>3.56</v>
+        <v>1.96</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="AK5">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-08-04 16:15:00</t>
+          <t>2026-08-04 14:30:00</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-04 19:00:00</t>
+          <t>2026-08-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,156 +1403,1297 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sparta Praha</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Olympique Lyonnais</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>3.6</v>
+      </c>
+      <c r="P7">
+        <v>1.87</v>
+      </c>
+      <c r="Q7">
+        <v>4</v>
+      </c>
+      <c r="R7">
+        <v>2.3</v>
+      </c>
+      <c r="S7">
+        <v>1.35</v>
+      </c>
+      <c r="T7">
+        <v>2.94</v>
+      </c>
+      <c r="U7">
+        <v>2.63</v>
+      </c>
+      <c r="V7">
+        <v>1.44</v>
+      </c>
+      <c r="W7">
+        <v>1.1</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.22</v>
+      </c>
+      <c r="Z7">
+        <v>3.54</v>
+      </c>
+      <c r="AA7">
+        <v>1.86</v>
+      </c>
+      <c r="AB7">
+        <v>1.99</v>
+      </c>
+      <c r="AC7">
+        <v>2.85</v>
+      </c>
+      <c r="AD7">
+        <v>1.33</v>
+      </c>
+      <c r="AE7">
+        <v>1.11</v>
+      </c>
+      <c r="AF7">
+        <v>1.7</v>
+      </c>
+      <c r="AG7">
+        <v>2.04</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.25</v>
+      </c>
+      <c r="AK7">
+        <v>1.2</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-1</v>
+      </c>
+      <c r="AN7">
+        <v>-1</v>
+      </c>
+      <c r="AO7">
+        <v>-1</v>
+      </c>
+      <c r="AP7">
+        <v>-1</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NEC</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>2.14</v>
+      </c>
+      <c r="R8">
+        <v>2.15</v>
+      </c>
+      <c r="S8">
+        <v>1.38</v>
+      </c>
+      <c r="T8">
+        <v>2.81</v>
+      </c>
+      <c r="U8">
+        <v>2.63</v>
+      </c>
+      <c r="V8">
+        <v>1.44</v>
+      </c>
+      <c r="W8">
+        <v>1.07</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>1.23</v>
+      </c>
+      <c r="Z8">
+        <v>3.5</v>
+      </c>
+      <c r="AA8">
+        <v>1.86</v>
+      </c>
+      <c r="AB8">
+        <v>1.98</v>
+      </c>
+      <c r="AC8">
+        <v>2.83</v>
+      </c>
+      <c r="AD8">
+        <v>1.33</v>
+      </c>
+      <c r="AE8">
+        <v>1.1</v>
+      </c>
+      <c r="AF8">
+        <v>1.84</v>
+      </c>
+      <c r="AG8">
+        <v>1.86</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.27</v>
+      </c>
+      <c r="AK8">
+        <v>2.31</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-1</v>
+      </c>
+      <c r="AN8">
+        <v>-1</v>
+      </c>
+      <c r="AO8">
+        <v>-1</v>
+      </c>
+      <c r="AP8">
+        <v>-1</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kauno Žalgiris</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N9">
+        <v>1.2</v>
+      </c>
+      <c r="O9">
+        <v>6</v>
+      </c>
+      <c r="P9">
+        <v>19</v>
+      </c>
+      <c r="Q9">
+        <v>1.65</v>
+      </c>
+      <c r="R9">
+        <v>2.63</v>
+      </c>
+      <c r="S9">
+        <v>1.36</v>
+      </c>
+      <c r="T9">
+        <v>2.89</v>
+      </c>
+      <c r="U9">
+        <v>2.59</v>
+      </c>
+      <c r="V9">
+        <v>1.44</v>
+      </c>
+      <c r="W9">
+        <v>1.06</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1.22</v>
+      </c>
+      <c r="Z9">
+        <v>3.54</v>
+      </c>
+      <c r="AA9">
+        <v>1.82</v>
+      </c>
+      <c r="AB9">
+        <v>1.99</v>
+      </c>
+      <c r="AC9">
+        <v>2.88</v>
+      </c>
+      <c r="AD9">
+        <v>1.34</v>
+      </c>
+      <c r="AE9">
+        <v>1.12</v>
+      </c>
+      <c r="AF9">
+        <v>2.5</v>
+      </c>
+      <c r="AG9">
+        <v>1.44</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.1</v>
+      </c>
+      <c r="AK9">
+        <v>4.1</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-1</v>
+      </c>
+      <c r="AN9">
+        <v>-1</v>
+      </c>
+      <c r="AO9">
+        <v>-1</v>
+      </c>
+      <c r="AP9">
+        <v>-1</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Thór</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N10">
+        <v>4.79</v>
+      </c>
+      <c r="O10">
+        <v>4.55</v>
+      </c>
+      <c r="P10">
+        <v>1.55</v>
+      </c>
+      <c r="Q10">
+        <v>3.5</v>
+      </c>
+      <c r="R10">
+        <v>2.54</v>
+      </c>
+      <c r="S10">
+        <v>1.15</v>
+      </c>
+      <c r="T10">
+        <v>4.35</v>
+      </c>
+      <c r="U10">
+        <v>1.9</v>
+      </c>
+      <c r="V10">
+        <v>1.98</v>
+      </c>
+      <c r="W10">
+        <v>1.22</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.04</v>
+      </c>
+      <c r="Z10">
+        <v>6.95</v>
+      </c>
+      <c r="AA10">
+        <v>1.33</v>
+      </c>
+      <c r="AB10">
+        <v>3.08</v>
+      </c>
+      <c r="AC10">
+        <v>1.8</v>
+      </c>
+      <c r="AD10">
+        <v>2</v>
+      </c>
+      <c r="AE10">
+        <v>1.35</v>
+      </c>
+      <c r="AF10">
+        <v>1.35</v>
+      </c>
+      <c r="AG10">
+        <v>2.94</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>2.03</v>
+      </c>
+      <c r="AK10">
+        <v>1.22</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>-1</v>
+      </c>
+      <c r="AN10">
+        <v>-1</v>
+      </c>
+      <c r="AO10">
+        <v>-1</v>
+      </c>
+      <c r="AP10">
+        <v>-1</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2026-08-04 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-1</v>
+      </c>
+      <c r="AN11">
+        <v>-1</v>
+      </c>
+      <c r="AO11">
+        <v>-1</v>
+      </c>
+      <c r="AP11">
+        <v>-1</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>2.12</v>
+      </c>
+      <c r="O12">
+        <v>4.2</v>
+      </c>
+      <c r="P12">
+        <v>2.76</v>
+      </c>
+      <c r="Q12">
+        <v>2.82</v>
+      </c>
+      <c r="R12">
+        <v>2.57</v>
+      </c>
+      <c r="S12">
+        <v>1.14</v>
+      </c>
+      <c r="T12">
+        <v>4.45</v>
+      </c>
+      <c r="U12">
+        <v>1.71</v>
+      </c>
+      <c r="V12">
+        <v>1.94</v>
+      </c>
+      <c r="W12">
+        <v>1.3</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>1.03</v>
+      </c>
+      <c r="Z12">
+        <v>7.2</v>
+      </c>
+      <c r="AA12">
+        <v>1.28</v>
+      </c>
+      <c r="AB12">
+        <v>3.34</v>
+      </c>
+      <c r="AC12">
+        <v>1.64</v>
+      </c>
+      <c r="AD12">
+        <v>2.04</v>
+      </c>
+      <c r="AE12">
+        <v>1.5</v>
+      </c>
+      <c r="AF12">
+        <v>1.25</v>
+      </c>
+      <c r="AG12">
+        <v>3.56</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.17</v>
+      </c>
+      <c r="AK12">
+        <v>1.51</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-1</v>
+      </c>
+      <c r="AN12">
+        <v>-1</v>
+      </c>
+      <c r="AO12">
+        <v>-1</v>
+      </c>
+      <c r="AP12">
+        <v>-1</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-08-04 16:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1</v>
+      </c>
+      <c r="AN13">
+        <v>-1</v>
+      </c>
+      <c r="AO13">
+        <v>-1</v>
+      </c>
+      <c r="AP13">
+        <v>-1</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-08-04 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Guabirá</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Real Tomayapo</t>
         </is>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>-1</v>
-      </c>
-      <c r="AN7">
-        <v>-1</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>-1</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1</v>
+      </c>
+      <c r="AN14">
+        <v>-1</v>
+      </c>
+      <c r="AO14">
+        <v>-1</v>
+      </c>
+      <c r="AP14">
+        <v>-1</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
         <is>
           <t>2026-08-04 21:00:00</t>
         </is>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P4">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q4">
-        <v>2.33</v>
+        <v>3.74</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U4">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
+        <v>1.05</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>1.28</v>
+      </c>
+      <c r="Z4">
+        <v>3.15</v>
+      </c>
+      <c r="AA4">
+        <v>2.02</v>
+      </c>
+      <c r="AB4">
+        <v>1.83</v>
+      </c>
+      <c r="AC4">
+        <v>3.3</v>
+      </c>
+      <c r="AD4">
+        <v>1.25</v>
+      </c>
+      <c r="AE4">
         <v>1.06</v>
       </c>
-      <c r="X4">
-        <v>1.02</v>
-      </c>
-      <c r="Y4">
+      <c r="AF4">
+        <v>1.72</v>
+      </c>
+      <c r="AG4">
+        <v>1.96</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.67</v>
+      </c>
+      <c r="AK4">
         <v>1.3</v>
-      </c>
-      <c r="Z4">
-        <v>2.99</v>
-      </c>
-      <c r="AA4">
-        <v>2.03</v>
-      </c>
-      <c r="AB4">
-        <v>1.76</v>
-      </c>
-      <c r="AC4">
-        <v>3.38</v>
-      </c>
-      <c r="AD4">
-        <v>1.24</v>
-      </c>
-      <c r="AE4">
-        <v>1.07</v>
-      </c>
-      <c r="AF4">
-        <v>1.87</v>
-      </c>
-      <c r="AG4">
-        <v>1.81</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.27</v>
-      </c>
-      <c r="AK4">
-        <v>1.87</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P5">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q5">
-        <v>3.74</v>
+        <v>2.33</v>
       </c>
       <c r="R5">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="S5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="AA5">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB5">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AC5">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AD5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AG5">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="Q6">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>4.3</v>
+        <v>3.54</v>
       </c>
       <c r="AA6">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AB6">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="AC6">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AD6">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.61</v>
+        <v>1.2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>2.14</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="U7">
         <v>2.63</v>
@@ -1477,37 +1477,37 @@
         <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z7">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA7">
         <v>1.86</v>
       </c>
       <c r="AB7">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC7">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="AD7">
         <v>1.33</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AG7">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.2</v>
+        <v>2.31</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q8">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="R8">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="S8">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="U8">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="V8">
         <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA8">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AB8">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC8">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE8">
+        <v>1.12</v>
+      </c>
+      <c r="AF8">
+        <v>2.5</v>
+      </c>
+      <c r="AG8">
+        <v>1.44</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.1</v>
       </c>
-      <c r="AF8">
-        <v>1.84</v>
-      </c>
-      <c r="AG8">
-        <v>1.86</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.27</v>
-      </c>
       <c r="AK8">
-        <v>2.31</v>
+        <v>4.1</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.2</v>
+        <v>2.27</v>
       </c>
       <c r="O9">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>19</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>1.65</v>
+        <v>2.65</v>
       </c>
       <c r="R9">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T9">
-        <v>2.89</v>
+        <v>3.15</v>
       </c>
       <c r="U9">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z9">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="AA9">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AB9">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="AC9">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD9">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AG9">
-        <v>1.44</v>
+        <v>2.38</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>4.1</v>
+        <v>1.61</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.92</v>
+        <v>1.91</v>
       </c>
       <c r="O2">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="P2">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="Q2">
-        <v>3.54</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
-        <v>2.89</v>
+        <v>2.56</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="Z2">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="AA2">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AB2">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="AC2">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="AD2">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.9</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="P3">
-        <v>3.8</v>
+        <v>2.17</v>
       </c>
       <c r="Q3">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="R3">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="S3">
+        <v>1.36</v>
+      </c>
+      <c r="T3">
+        <v>2.88</v>
+      </c>
+      <c r="U3">
+        <v>2.73</v>
+      </c>
+      <c r="V3">
+        <v>1.36</v>
+      </c>
+      <c r="W3">
+        <v>1.06</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1.3</v>
+      </c>
+      <c r="Z3">
+        <v>3.15</v>
+      </c>
+      <c r="AA3">
+        <v>1.96</v>
+      </c>
+      <c r="AB3">
+        <v>1.79</v>
+      </c>
+      <c r="AC3">
+        <v>3.44</v>
+      </c>
+      <c r="AD3">
+        <v>1.23</v>
+      </c>
+      <c r="AE3">
+        <v>1.11</v>
+      </c>
+      <c r="AF3">
+        <v>1.73</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.29</v>
+      </c>
+      <c r="AK3">
         <v>1.33</v>
-      </c>
-      <c r="T3">
-        <v>3.04</v>
-      </c>
-      <c r="U3">
-        <v>2.56</v>
-      </c>
-      <c r="V3">
-        <v>1.44</v>
-      </c>
-      <c r="W3">
-        <v>1.07</v>
-      </c>
-      <c r="X3">
-        <v>1.01</v>
-      </c>
-      <c r="Y3">
-        <v>1.23</v>
-      </c>
-      <c r="Z3">
-        <v>3.6</v>
-      </c>
-      <c r="AA3">
-        <v>1.79</v>
-      </c>
-      <c r="AB3">
-        <v>1.99</v>
-      </c>
-      <c r="AC3">
-        <v>2.88</v>
-      </c>
-      <c r="AD3">
-        <v>1.34</v>
-      </c>
-      <c r="AE3">
-        <v>1.12</v>
-      </c>
-      <c r="AF3">
-        <v>1.68</v>
-      </c>
-      <c r="AG3">
-        <v>2.04</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.22</v>
-      </c>
-      <c r="AK3">
-        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>1.81</v>
       </c>
       <c r="O4">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="P4">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>3.74</v>
+        <v>2.33</v>
       </c>
       <c r="R4">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T4">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z4">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="AA4">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB4">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AC4">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE4">
         <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q5">
-        <v>2.33</v>
+        <v>3.31</v>
       </c>
       <c r="R5">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="U5">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W5">
+        <v>1.05</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.28</v>
+      </c>
+      <c r="Z5">
+        <v>3.25</v>
+      </c>
+      <c r="AA5">
+        <v>2.02</v>
+      </c>
+      <c r="AB5">
+        <v>1.83</v>
+      </c>
+      <c r="AC5">
+        <v>3.3</v>
+      </c>
+      <c r="AD5">
+        <v>1.38</v>
+      </c>
+      <c r="AE5">
         <v>1.06</v>
       </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
+      <c r="AF5">
+        <v>1.76</v>
+      </c>
+      <c r="AG5">
+        <v>2.05</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.67</v>
+      </c>
+      <c r="AK5">
         <v>1.3</v>
-      </c>
-      <c r="Z5">
-        <v>2.99</v>
-      </c>
-      <c r="AA5">
-        <v>2.03</v>
-      </c>
-      <c r="AB5">
-        <v>1.76</v>
-      </c>
-      <c r="AC5">
-        <v>3.38</v>
-      </c>
-      <c r="AD5">
-        <v>1.24</v>
-      </c>
-      <c r="AE5">
-        <v>1.07</v>
-      </c>
-      <c r="AF5">
-        <v>1.87</v>
-      </c>
-      <c r="AG5">
-        <v>1.81</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.27</v>
-      </c>
-      <c r="AK5">
-        <v>1.87</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>1.99</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P6">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z6">
-        <v>3.54</v>
+        <v>4.3</v>
       </c>
       <c r="AA6">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AB6">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="AC6">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.2</v>
+        <v>1.61</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q7">
-        <v>2.14</v>
+        <v>1.62</v>
       </c>
       <c r="R7">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="S7">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.81</v>
+        <v>3.08</v>
       </c>
       <c r="U7">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA7">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AB7">
         <v>1.98</v>
       </c>
       <c r="AC7">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AD7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE7">
+        <v>1.12</v>
+      </c>
+      <c r="AF7">
+        <v>2.5</v>
+      </c>
+      <c r="AG7">
+        <v>1.44</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.1</v>
       </c>
-      <c r="AF7">
-        <v>1.84</v>
-      </c>
-      <c r="AG7">
-        <v>1.86</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.27</v>
-      </c>
       <c r="AK7">
-        <v>2.31</v>
+        <v>4.45</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="R8">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.54</v>
+        <v>4.03</v>
       </c>
       <c r="AA8">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="AC8">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AD8">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG8">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK8">
-        <v>4.1</v>
+        <v>2.48</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.27</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="Q9">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="R9">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="U9">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>4.3</v>
+        <v>3.86</v>
       </c>
       <c r="AA9">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AB9">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="AC9">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AD9">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
+        <v>1.22</v>
+      </c>
+      <c r="AK9">
         <v>1.29</v>
-      </c>
-      <c r="AK9">
-        <v>1.61</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.91</v>
+        <v>2.92</v>
       </c>
       <c r="O2">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="P2">
+        <v>2.17</v>
+      </c>
+      <c r="Q2">
+        <v>3.5</v>
+      </c>
+      <c r="R2">
+        <v>2.03</v>
+      </c>
+      <c r="S2">
+        <v>1.36</v>
+      </c>
+      <c r="T2">
+        <v>2.88</v>
+      </c>
+      <c r="U2">
+        <v>2.73</v>
+      </c>
+      <c r="V2">
+        <v>1.36</v>
+      </c>
+      <c r="W2">
+        <v>1.06</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1.3</v>
+      </c>
+      <c r="Z2">
         <v>3.15</v>
       </c>
-      <c r="Q2">
-        <v>2.4</v>
-      </c>
-      <c r="R2">
-        <v>2.3</v>
-      </c>
-      <c r="S2">
-        <v>1.3</v>
-      </c>
-      <c r="T2">
-        <v>3.2</v>
-      </c>
-      <c r="U2">
-        <v>2.56</v>
-      </c>
-      <c r="V2">
-        <v>1.45</v>
-      </c>
-      <c r="W2">
-        <v>1.07</v>
-      </c>
-      <c r="X2">
-        <v>1.02</v>
-      </c>
-      <c r="Y2">
+      <c r="AA2">
+        <v>1.96</v>
+      </c>
+      <c r="AB2">
+        <v>1.79</v>
+      </c>
+      <c r="AC2">
+        <v>3.44</v>
+      </c>
+      <c r="AD2">
         <v>1.23</v>
       </c>
-      <c r="Z2">
-        <v>3.6</v>
-      </c>
-      <c r="AA2">
-        <v>1.79</v>
-      </c>
-      <c r="AB2">
-        <v>1.99</v>
-      </c>
-      <c r="AC2">
-        <v>2.88</v>
-      </c>
-      <c r="AD2">
-        <v>1.34</v>
-      </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>1.91</v>
       </c>
       <c r="O3">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="P3">
-        <v>2.17</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
+        <v>3.2</v>
+      </c>
+      <c r="U3">
+        <v>2.56</v>
+      </c>
+      <c r="V3">
+        <v>1.45</v>
+      </c>
+      <c r="W3">
+        <v>1.07</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
+        <v>1.23</v>
+      </c>
+      <c r="Z3">
+        <v>3.6</v>
+      </c>
+      <c r="AA3">
+        <v>1.79</v>
+      </c>
+      <c r="AB3">
+        <v>1.99</v>
+      </c>
+      <c r="AC3">
         <v>2.88</v>
       </c>
-      <c r="U3">
-        <v>2.73</v>
-      </c>
-      <c r="V3">
-        <v>1.36</v>
-      </c>
-      <c r="W3">
-        <v>1.06</v>
-      </c>
-      <c r="X3">
-        <v>1</v>
-      </c>
-      <c r="Y3">
-        <v>1.3</v>
-      </c>
-      <c r="Z3">
-        <v>3.15</v>
-      </c>
-      <c r="AA3">
-        <v>1.96</v>
-      </c>
-      <c r="AB3">
-        <v>1.79</v>
-      </c>
-      <c r="AC3">
-        <v>3.44</v>
-      </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
+        <v>3.4</v>
+      </c>
+      <c r="O6">
+        <v>3.7</v>
+      </c>
+      <c r="P6">
+        <v>1.87</v>
+      </c>
+      <c r="Q6">
+        <v>4</v>
+      </c>
+      <c r="R6">
+        <v>2.3</v>
+      </c>
+      <c r="S6">
+        <v>1.32</v>
+      </c>
+      <c r="T6">
+        <v>3.11</v>
+      </c>
+      <c r="U6">
+        <v>2.63</v>
+      </c>
+      <c r="V6">
+        <v>1.44</v>
+      </c>
+      <c r="W6">
+        <v>1.11</v>
+      </c>
+      <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>1.22</v>
+      </c>
+      <c r="Z6">
+        <v>3.86</v>
+      </c>
+      <c r="AA6">
+        <v>1.86</v>
+      </c>
+      <c r="AB6">
         <v>1.99</v>
       </c>
-      <c r="O6">
-        <v>3.55</v>
-      </c>
-      <c r="P6">
-        <v>3</v>
-      </c>
-      <c r="Q6">
-        <v>2.65</v>
-      </c>
-      <c r="R6">
-        <v>2.35</v>
-      </c>
-      <c r="S6">
-        <v>1.3</v>
-      </c>
-      <c r="T6">
-        <v>3.1</v>
-      </c>
-      <c r="U6">
-        <v>2.25</v>
-      </c>
-      <c r="V6">
-        <v>1.57</v>
-      </c>
-      <c r="W6">
-        <v>1.13</v>
-      </c>
-      <c r="X6">
-        <v>1.02</v>
-      </c>
-      <c r="Y6">
-        <v>1.15</v>
-      </c>
-      <c r="Z6">
-        <v>4.3</v>
-      </c>
-      <c r="AA6">
-        <v>1.58</v>
-      </c>
-      <c r="AB6">
-        <v>2.16</v>
-      </c>
       <c r="AC6">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AD6">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
+        <v>1.22</v>
+      </c>
+      <c r="AK6">
         <v>1.29</v>
-      </c>
-      <c r="AK6">
-        <v>1.61</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="R7">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="V7">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z7">
-        <v>3.54</v>
+        <v>4.03</v>
       </c>
       <c r="AA7">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB7">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AC7">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AD7">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG7">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK7">
-        <v>4.45</v>
+        <v>2.48</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q8">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="R8">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="S8">
+        <v>1.3</v>
+      </c>
+      <c r="T8">
+        <v>3.1</v>
+      </c>
+      <c r="U8">
+        <v>2.25</v>
+      </c>
+      <c r="V8">
+        <v>1.57</v>
+      </c>
+      <c r="W8">
+        <v>1.13</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>1.15</v>
+      </c>
+      <c r="Z8">
+        <v>4.3</v>
+      </c>
+      <c r="AA8">
+        <v>1.58</v>
+      </c>
+      <c r="AB8">
+        <v>2.16</v>
+      </c>
+      <c r="AC8">
+        <v>2.45</v>
+      </c>
+      <c r="AD8">
+        <v>1.46</v>
+      </c>
+      <c r="AE8">
+        <v>1.17</v>
+      </c>
+      <c r="AF8">
+        <v>1.5</v>
+      </c>
+      <c r="AG8">
+        <v>2.38</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.29</v>
       </c>
-      <c r="T8">
-        <v>3.25</v>
-      </c>
-      <c r="U8">
-        <v>2.47</v>
-      </c>
-      <c r="V8">
-        <v>1.48</v>
-      </c>
-      <c r="W8">
-        <v>1.08</v>
-      </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
-      <c r="Y8">
-        <v>1.19</v>
-      </c>
-      <c r="Z8">
-        <v>4.03</v>
-      </c>
-      <c r="AA8">
-        <v>1.75</v>
-      </c>
-      <c r="AB8">
-        <v>2.12</v>
-      </c>
-      <c r="AC8">
-        <v>2.77</v>
-      </c>
-      <c r="AD8">
-        <v>1.41</v>
-      </c>
-      <c r="AE8">
-        <v>1.15</v>
-      </c>
-      <c r="AF8">
-        <v>1.79</v>
-      </c>
-      <c r="AG8">
-        <v>1.91</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.23</v>
-      </c>
       <c r="AK8">
-        <v>2.48</v>
+        <v>1.61</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P9">
-        <v>1.87</v>
+        <v>13</v>
       </c>
       <c r="Q9">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="U9">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.86</v>
+        <v>3.54</v>
       </c>
       <c r="AA9">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AB9">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC9">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AD9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG9">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK9">
-        <v>1.29</v>
+        <v>4.45</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="R7">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="S7">
+        <v>1.3</v>
+      </c>
+      <c r="T7">
+        <v>3.1</v>
+      </c>
+      <c r="U7">
+        <v>2.25</v>
+      </c>
+      <c r="V7">
+        <v>1.57</v>
+      </c>
+      <c r="W7">
+        <v>1.13</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.15</v>
+      </c>
+      <c r="Z7">
+        <v>4.3</v>
+      </c>
+      <c r="AA7">
+        <v>1.58</v>
+      </c>
+      <c r="AB7">
+        <v>2.16</v>
+      </c>
+      <c r="AC7">
+        <v>2.45</v>
+      </c>
+      <c r="AD7">
+        <v>1.46</v>
+      </c>
+      <c r="AE7">
+        <v>1.17</v>
+      </c>
+      <c r="AF7">
+        <v>1.5</v>
+      </c>
+      <c r="AG7">
+        <v>2.38</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.29</v>
       </c>
-      <c r="T7">
-        <v>3.25</v>
-      </c>
-      <c r="U7">
-        <v>2.47</v>
-      </c>
-      <c r="V7">
-        <v>1.48</v>
-      </c>
-      <c r="W7">
-        <v>1.08</v>
-      </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>1.19</v>
-      </c>
-      <c r="Z7">
-        <v>4.03</v>
-      </c>
-      <c r="AA7">
-        <v>1.75</v>
-      </c>
-      <c r="AB7">
-        <v>2.12</v>
-      </c>
-      <c r="AC7">
-        <v>2.77</v>
-      </c>
-      <c r="AD7">
-        <v>1.41</v>
-      </c>
-      <c r="AE7">
-        <v>1.15</v>
-      </c>
-      <c r="AF7">
-        <v>1.79</v>
-      </c>
-      <c r="AG7">
-        <v>1.91</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.23</v>
-      </c>
       <c r="AK7">
-        <v>2.48</v>
+        <v>1.61</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Q8">
-        <v>2.65</v>
+        <v>1.62</v>
       </c>
       <c r="R8">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U8">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>4.3</v>
+        <v>3.54</v>
       </c>
       <c r="AA8">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AB8">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="AC8">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AD8">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AG8">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AK8">
-        <v>1.61</v>
+        <v>4.45</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="R9">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="V9">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>3.54</v>
+        <v>4.03</v>
       </c>
       <c r="AA9">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB9">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AC9">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AD9">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG9">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>4.45</v>
+        <v>2.48</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.92</v>
+        <v>1.91</v>
       </c>
       <c r="O2">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="P2">
-        <v>2.17</v>
+        <v>3.15</v>
       </c>
       <c r="Q2">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="R2">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
+        <v>3.2</v>
+      </c>
+      <c r="U2">
+        <v>2.56</v>
+      </c>
+      <c r="V2">
+        <v>1.45</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1.02</v>
+      </c>
+      <c r="Y2">
+        <v>1.23</v>
+      </c>
+      <c r="Z2">
+        <v>3.6</v>
+      </c>
+      <c r="AA2">
+        <v>1.79</v>
+      </c>
+      <c r="AB2">
+        <v>1.99</v>
+      </c>
+      <c r="AC2">
         <v>2.88</v>
       </c>
-      <c r="U2">
-        <v>2.73</v>
-      </c>
-      <c r="V2">
-        <v>1.36</v>
-      </c>
-      <c r="W2">
-        <v>1.06</v>
-      </c>
-      <c r="X2">
-        <v>1</v>
-      </c>
-      <c r="Y2">
-        <v>1.3</v>
-      </c>
-      <c r="Z2">
-        <v>3.15</v>
-      </c>
-      <c r="AA2">
-        <v>1.96</v>
-      </c>
-      <c r="AB2">
-        <v>1.79</v>
-      </c>
-      <c r="AC2">
-        <v>3.44</v>
-      </c>
       <c r="AD2">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.91</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="P3">
+        <v>2.17</v>
+      </c>
+      <c r="Q3">
+        <v>3.5</v>
+      </c>
+      <c r="R3">
+        <v>2.03</v>
+      </c>
+      <c r="S3">
+        <v>1.36</v>
+      </c>
+      <c r="T3">
+        <v>2.88</v>
+      </c>
+      <c r="U3">
+        <v>2.73</v>
+      </c>
+      <c r="V3">
+        <v>1.36</v>
+      </c>
+      <c r="W3">
+        <v>1.06</v>
+      </c>
+      <c r="X3">
+        <v>1</v>
+      </c>
+      <c r="Y3">
+        <v>1.3</v>
+      </c>
+      <c r="Z3">
         <v>3.15</v>
       </c>
-      <c r="Q3">
-        <v>2.4</v>
-      </c>
-      <c r="R3">
-        <v>2.3</v>
-      </c>
-      <c r="S3">
-        <v>1.3</v>
-      </c>
-      <c r="T3">
-        <v>3.2</v>
-      </c>
-      <c r="U3">
-        <v>2.56</v>
-      </c>
-      <c r="V3">
-        <v>1.45</v>
-      </c>
-      <c r="W3">
-        <v>1.07</v>
-      </c>
-      <c r="X3">
-        <v>1.02</v>
-      </c>
-      <c r="Y3">
+      <c r="AA3">
+        <v>1.96</v>
+      </c>
+      <c r="AB3">
+        <v>1.79</v>
+      </c>
+      <c r="AC3">
+        <v>3.44</v>
+      </c>
+      <c r="AD3">
         <v>1.23</v>
       </c>
-      <c r="Z3">
-        <v>3.6</v>
-      </c>
-      <c r="AA3">
-        <v>1.79</v>
-      </c>
-      <c r="AB3">
-        <v>1.99</v>
-      </c>
-      <c r="AC3">
-        <v>2.88</v>
-      </c>
-      <c r="AD3">
-        <v>1.34</v>
-      </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -635,28 +635,28 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="O2">
-        <v>3.65</v>
+        <v>3.09</v>
       </c>
       <c r="P2">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="Q2">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S2">
         <v>1.3</v>
       </c>
       <c r="T2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U2">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="V2">
         <v>1.45</v>
@@ -665,34 +665,34 @@
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z2">
         <v>3.6</v>
       </c>
       <c r="AA2">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB2">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AC2">
         <v>2.88</v>
       </c>
       <c r="AD2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="O3">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="P3">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R3">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U3">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AA3">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB3">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE3">
         <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG3">
         <v>2</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK3">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,28 +961,28 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.81</v>
+        <v>1.59</v>
       </c>
       <c r="O4">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="Q4">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S4">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
         <v>2.88</v>
       </c>
       <c r="U4">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="V4">
         <v>1.36</v>
@@ -991,34 +991,34 @@
         <v>1.06</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>2.99</v>
+        <v>2.82</v>
       </c>
       <c r="AA4">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC4">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AD4">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF4">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,61 +1124,61 @@
         </is>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P5">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Q5">
-        <v>3.31</v>
+        <v>4.3</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="U5">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="V5">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W5">
+        <v>1.08</v>
+      </c>
+      <c r="X5">
         <v>1.05</v>
       </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AA5">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AB5">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
         <v>2.05</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AK5">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="Q6">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T6">
-        <v>3.11</v>
+        <v>2.89</v>
       </c>
       <c r="U6">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA6">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AB6">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC6">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AK6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="O7">
+        <v>3.7</v>
+      </c>
+      <c r="P7">
+        <v>3.2</v>
+      </c>
+      <c r="Q7">
+        <v>2.6</v>
+      </c>
+      <c r="R7">
+        <v>2.3</v>
+      </c>
+      <c r="S7">
+        <v>1.28</v>
+      </c>
+      <c r="T7">
         <v>3.55</v>
       </c>
-      <c r="P7">
-        <v>3</v>
-      </c>
-      <c r="Q7">
-        <v>2.65</v>
-      </c>
-      <c r="R7">
-        <v>2.35</v>
-      </c>
-      <c r="S7">
-        <v>1.3</v>
-      </c>
-      <c r="T7">
-        <v>3.1</v>
-      </c>
       <c r="U7">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W7">
         <v>1.13</v>
@@ -1492,19 +1492,19 @@
         <v>1.58</v>
       </c>
       <c r="AB7">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC7">
         <v>2.45</v>
       </c>
       <c r="AD7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG7">
         <v>2.38</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK7">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="O8">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q8">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="R8">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="U8">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="V8">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
+        <v>1.13</v>
+      </c>
+      <c r="Z8">
+        <v>4.88</v>
+      </c>
+      <c r="AA8">
+        <v>1.53</v>
+      </c>
+      <c r="AB8">
+        <v>2.51</v>
+      </c>
+      <c r="AC8">
+        <v>2.38</v>
+      </c>
+      <c r="AD8">
+        <v>1.55</v>
+      </c>
+      <c r="AE8">
         <v>1.22</v>
       </c>
-      <c r="Z8">
-        <v>3.54</v>
-      </c>
-      <c r="AA8">
-        <v>1.83</v>
-      </c>
-      <c r="AB8">
-        <v>1.98</v>
-      </c>
-      <c r="AC8">
-        <v>2.8</v>
-      </c>
-      <c r="AD8">
-        <v>1.34</v>
-      </c>
-      <c r="AE8">
-        <v>1.12</v>
-      </c>
       <c r="AF8">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AG8">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK8">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>2.02</v>
@@ -1791,19 +1791,19 @@
         <v>2.29</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
         <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="V9">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
         <v>1.04</v>
@@ -1812,28 +1812,28 @@
         <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>4.03</v>
+        <v>3.8</v>
       </c>
       <c r="AA9">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AC9">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AD9">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
         <v>1.79</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.79</v>
+        <v>4</v>
       </c>
       <c r="O10">
-        <v>4.55</v>
+        <v>4.25</v>
       </c>
       <c r="P10">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Q10">
-        <v>3.5</v>
+        <v>4.26</v>
       </c>
       <c r="R10">
-        <v>2.54</v>
+        <v>2.85</v>
       </c>
       <c r="S10">
         <v>1.15</v>
       </c>
       <c r="T10">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="U10">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V10">
         <v>1.98</v>
       </c>
       <c r="W10">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1975,28 +1975,28 @@
         <v>1.04</v>
       </c>
       <c r="Z10">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="AA10">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AB10">
         <v>3.08</v>
       </c>
       <c r="AC10">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AE10">
         <v>1.35</v>
       </c>
       <c r="AF10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AG10">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>2.03</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P12">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="Q12">
         <v>2.82</v>
@@ -2283,46 +2283,46 @@
         <v>1.14</v>
       </c>
       <c r="T12">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="U12">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="V12">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Z12">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AA12">
         <v>1.28</v>
       </c>
       <c r="AB12">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AC12">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AD12">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AE12">
         <v>1.5</v>
       </c>
       <c r="AF12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG12">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.52</v>
       </c>
       <c r="AK12">
         <v>1.51</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU14"/>
+  <dimension ref="A1:AU13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1942,7 +1942,7 @@
         <v>4</v>
       </c>
       <c r="O10">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="P10">
         <v>1.67</v>
@@ -1951,7 +1951,7 @@
         <v>4.26</v>
       </c>
       <c r="R10">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="S10">
         <v>1.15</v>
@@ -1960,10 +1960,10 @@
         <v>4.4</v>
       </c>
       <c r="U10">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V10">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="W10">
         <v>1.21</v>
@@ -1978,16 +1978,16 @@
         <v>7.1</v>
       </c>
       <c r="AA10">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AB10">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="AC10">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AD10">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AE10">
         <v>1.35</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
         <v>1.19</v>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-08-04 16:15:00</t>
+          <t>2026-08-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G13">
@@ -2531,169 +2531,6 @@
         <v>0</v>
       </c>
       <c r="AU13" t="inlineStr">
-        <is>
-          <t>2026-08-04 19:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Guabirá</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Real Tomayapo</t>
-        </is>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>-1</v>
-      </c>
-      <c r="AN14">
-        <v>-1</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>-1</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
         <is>
           <t>2026-08-04 21:00:00</t>
         </is>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.89</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="P2">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q2">
-        <v>2.38</v>
+        <v>3.45</v>
       </c>
       <c r="R2">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T2">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U2">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V2">
         <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y2">
         <v>1.25</v>
       </c>
       <c r="Z2">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA2">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB2">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC2">
-        <v>2.88</v>
+        <v>3.24</v>
       </c>
       <c r="AD2">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
         <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AK2">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.66</v>
+        <v>1.89</v>
       </c>
       <c r="O3">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="P3">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q3">
-        <v>3.45</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="S3">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U3">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
         <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC3">
-        <v>3.24</v>
+        <v>2.88</v>
       </c>
       <c r="AD3">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
         <v>1.7</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="O2">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q2">
         <v>3.45</v>
@@ -656,7 +656,7 @@
         <v>2.95</v>
       </c>
       <c r="U2">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="V2">
         <v>1.45</v>
@@ -668,31 +668,31 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AA2">
         <v>1.95</v>
       </c>
       <c r="AB2">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC2">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD2">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
         <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.57</v>
       </c>
       <c r="AK2">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="O3">
-        <v>3.09</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -813,49 +813,49 @@
         <v>2.27</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
         <v>3.1</v>
       </c>
       <c r="U3">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="AA3">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="AD3">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK3">
         <v>1.73</v>
@@ -961,55 +961,55 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="O4">
-        <v>3.55</v>
+        <v>3.76</v>
       </c>
       <c r="P4">
-        <v>4.65</v>
+        <v>5.05</v>
       </c>
       <c r="Q4">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
         <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="AA4">
         <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC4">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AD4">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE4">
         <v>1.09</v>
@@ -1018,7 +1018,7 @@
         <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK4">
         <v>2.2</v>
@@ -1127,34 +1127,34 @@
         <v>3.8</v>
       </c>
       <c r="O5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
         <v>1.85</v>
       </c>
       <c r="Q5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="R5">
         <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
         <v>1.22</v>
@@ -1163,7 +1163,7 @@
         <v>3.65</v>
       </c>
       <c r="AA5">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB5">
         <v>2.05</v>
@@ -1172,16 +1172,16 @@
         <v>2.8</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
         <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AK5">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
         <v>2.11</v>
@@ -1302,46 +1302,46 @@
         <v>2.25</v>
       </c>
       <c r="S6">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T6">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="V6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
         <v>1.71</v>
       </c>
       <c r="AB6">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AC6">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
         <v>2.2</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AK6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,16 +1459,16 @@
         <v>3.2</v>
       </c>
       <c r="Q7">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S7">
         <v>1.28</v>
       </c>
       <c r="T7">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="U7">
         <v>2.2</v>
@@ -1489,10 +1489,10 @@
         <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB7">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
         <v>2.45</v>
@@ -1504,10 +1504,10 @@
         <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="O8">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="P8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q8">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="R8">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="U8">
         <v>2.27</v>
       </c>
       <c r="V8">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
         <v>1.12</v>
@@ -1646,31 +1646,31 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z8">
-        <v>4.88</v>
+        <v>5.25</v>
       </c>
       <c r="AA8">
         <v>1.53</v>
       </c>
       <c r="AB8">
-        <v>2.51</v>
+        <v>2.27</v>
       </c>
       <c r="AC8">
         <v>2.38</v>
       </c>
       <c r="AD8">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF8">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="AG8">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.07</v>
       </c>
       <c r="AK8">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,10 +1785,10 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="R9">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="S9">
         <v>1.33</v>
@@ -1797,7 +1797,7 @@
         <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V9">
         <v>1.5</v>
@@ -1812,28 +1812,28 @@
         <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AA9">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AC9">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD9">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
         <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG9">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK9">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O10">
         <v>4.3</v>
       </c>
       <c r="P10">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q10">
         <v>4.26</v>
@@ -1954,10 +1954,10 @@
         <v>2.57</v>
       </c>
       <c r="S10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T10">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>1.85</v>
@@ -1966,7 +1966,7 @@
         <v>1.85</v>
       </c>
       <c r="W10">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1981,13 +1981,13 @@
         <v>1.28</v>
       </c>
       <c r="AB10">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="AC10">
         <v>1.85</v>
       </c>
       <c r="AD10">
-        <v>1.93</v>
+        <v>2.17</v>
       </c>
       <c r="AE10">
         <v>1.35</v>
@@ -1996,7 +1996,7 @@
         <v>1.34</v>
       </c>
       <c r="AG10">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
         <v>1.19</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -641,25 +641,25 @@
         <v>3.3</v>
       </c>
       <c r="P2">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="Q2">
         <v>3.45</v>
       </c>
       <c r="R2">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
         <v>1.35</v>
       </c>
       <c r="T2">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U2">
         <v>2.55</v>
       </c>
       <c r="V2">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
         <v>1.08</v>
@@ -674,13 +674,13 @@
         <v>3.35</v>
       </c>
       <c r="AA2">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB2">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AC2">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD2">
         <v>1.31</v>
@@ -692,7 +692,7 @@
         <v>1.7</v>
       </c>
       <c r="AG2">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AK2">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P3">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
         <v>1.07</v>
@@ -831,7 +831,7 @@
         <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z3">
         <v>3.44</v>
@@ -840,7 +840,7 @@
         <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC3">
         <v>2.94</v>
@@ -967,28 +967,28 @@
         <v>3.76</v>
       </c>
       <c r="P4">
-        <v>5.05</v>
+        <v>5.35</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
       </c>
       <c r="R4">
-        <v>2.28</v>
+        <v>2.01</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T4">
         <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="V4">
         <v>1.38</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
         <v>1.06</v>
@@ -997,28 +997,28 @@
         <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA4">
         <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC4">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="AD4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1127,13 +1127,13 @@
         <v>3.8</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R5">
         <v>2.25</v>
@@ -1154,34 +1154,34 @@
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA5">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
         <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF5">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AK5">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
         <v>3.4</v>
@@ -1311,22 +1311,22 @@
         <v>2.45</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB6">
         <v>2.04</v>
@@ -1335,13 +1335,13 @@
         <v>3</v>
       </c>
       <c r="AD6">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG6">
         <v>2.2</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AK6">
         <v>1.33</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="O7">
         <v>3.7</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="Q7">
         <v>2.53</v>
@@ -1465,22 +1465,22 @@
         <v>2.39</v>
       </c>
       <c r="S7">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V7">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="W7">
         <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
         <v>1.15</v>
@@ -1501,13 +1501,13 @@
         <v>1.47</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG7">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>1.17</v>
       </c>
       <c r="O8">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="P8">
         <v>15</v>
       </c>
       <c r="Q8">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="R8">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="S8">
         <v>1.25</v>
@@ -1640,37 +1640,37 @@
         <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="AA8">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AC8">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD8">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE8">
         <v>1.2</v>
       </c>
       <c r="AF8">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AG8">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK8">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>5</v>
       </c>
       <c r="Q9">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
         <v>1.33</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="U9">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA9">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AB9">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC9">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AD9">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE9">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AK9">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.7</v>
+        <v>4.17</v>
       </c>
       <c r="O10">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P10">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="Q10">
         <v>4.26</v>
       </c>
       <c r="R10">
-        <v>2.57</v>
+        <v>2.85</v>
       </c>
       <c r="S10">
         <v>1.14</v>
@@ -1960,10 +1960,10 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="V10">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="W10">
         <v>1.22</v>
@@ -1972,31 +1972,31 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Z10">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB10">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AC10">
         <v>1.85</v>
       </c>
       <c r="AD10">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="AE10">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF10">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG10">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
         <v>1.19</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -1945,13 +1945,13 @@
         <v>4.1</v>
       </c>
       <c r="P10">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="Q10">
         <v>4.26</v>
       </c>
       <c r="R10">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="S10">
         <v>1.14</v>
@@ -1960,10 +1960,10 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="V10">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="W10">
         <v>1.22</v>
@@ -1972,31 +1972,31 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z10">
         <v>7</v>
       </c>
       <c r="AA10">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AB10">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="AC10">
         <v>1.85</v>
       </c>
       <c r="AD10">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AE10">
         <v>1.39</v>
       </c>
       <c r="AF10">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG10">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="O2">
         <v>3.3</v>
       </c>
       <c r="P2">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="Q2">
         <v>3.45</v>
@@ -656,10 +656,10 @@
         <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
         <v>1.08</v>
@@ -668,25 +668,25 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z2">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA2">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB2">
         <v>1.78</v>
       </c>
       <c r="AC2">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AD2">
         <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
         <v>1.7</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AK2">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>3.55</v>
       </c>
       <c r="P3">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
         <v>2.46</v>
@@ -813,7 +813,7 @@
         <v>2.23</v>
       </c>
       <c r="S3">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
         <v>3.2</v>
@@ -840,7 +840,7 @@
         <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC3">
         <v>2.94</v>
@@ -973,16 +973,16 @@
         <v>2.2</v>
       </c>
       <c r="R4">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
         <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V4">
         <v>1.38</v>
@@ -991,19 +991,19 @@
         <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AA4">
         <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC4">
         <v>3.55</v>
@@ -1015,10 +1015,10 @@
         <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1127,19 +1127,19 @@
         <v>3.8</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P5">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T5">
         <v>3.1</v>
@@ -1163,7 +1163,7 @@
         <v>3.7</v>
       </c>
       <c r="AA5">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB5">
         <v>2.05</v>
@@ -1172,10 +1172,10 @@
         <v>2.66</v>
       </c>
       <c r="AD5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
         <v>1.65</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
         <v>3.78</v>
@@ -1308,25 +1308,25 @@
         <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
         <v>2.04</v>
@@ -1338,7 +1338,7 @@
         <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
         <v>1.6</v>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="O7">
         <v>3.7</v>
@@ -1471,10 +1471,10 @@
         <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
         <v>1.13</v>
@@ -1486,7 +1486,7 @@
         <v>1.15</v>
       </c>
       <c r="Z7">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA7">
         <v>1.62</v>
@@ -1495,7 +1495,7 @@
         <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AD7">
         <v>1.47</v>
@@ -1504,10 +1504,10 @@
         <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         <v>1.17</v>
       </c>
       <c r="O8">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="P8">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q8">
         <v>1.55</v>
@@ -1634,7 +1634,7 @@
         <v>3.14</v>
       </c>
       <c r="U8">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="V8">
         <v>1.57</v>
@@ -1646,25 +1646,25 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z8">
-        <v>4.25</v>
+        <v>4.93</v>
       </c>
       <c r="AA8">
         <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC8">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD8">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
         <v>2.61</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="O9">
-        <v>3.77</v>
+        <v>4.33</v>
       </c>
       <c r="P9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q9">
         <v>2</v>
@@ -1800,10 +1800,10 @@
         <v>2.5</v>
       </c>
       <c r="V9">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1.04</v>
@@ -1821,13 +1821,13 @@
         <v>2.08</v>
       </c>
       <c r="AC9">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="AD9">
         <v>1.48</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
         <v>1.75</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
         <v>2.43</v>
@@ -1942,7 +1942,7 @@
         <v>4.17</v>
       </c>
       <c r="O10">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P10">
         <v>1.67</v>
@@ -1975,13 +1975,13 @@
         <v>1.04</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA10">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AB10">
-        <v>3.65</v>
+        <v>3.08</v>
       </c>
       <c r="AC10">
         <v>1.85</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q13">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -2111,55 +2111,55 @@
         <v>2.95</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA11">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AB11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
         <v>3.75</v>
@@ -2304,10 +2304,10 @@
         <v>5.3</v>
       </c>
       <c r="AA12">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AB12">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AC12">
         <v>2.17</v>
@@ -2437,55 +2437,55 @@
         <v>7.75</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O11">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="P11">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q11">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="S11">
         <v>1.14</v>
       </c>
       <c r="T11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>1.8</v>
@@ -2147,10 +2147,10 @@
         <v>3.5</v>
       </c>
       <c r="AC11">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AD11">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AE11">
         <v>1.44</v>
@@ -2175,7 +2175,7 @@
         <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q12">
         <v>3.05</v>
@@ -2338,7 +2338,7 @@
         <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O13">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="P13">
-        <v>7.75</v>
+        <v>7.47</v>
       </c>
       <c r="Q13">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R13">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
       <c r="S13">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T13">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U13">
+        <v>1.8</v>
+      </c>
+      <c r="V13">
         <v>1.91</v>
-      </c>
-      <c r="V13">
-        <v>1.79</v>
       </c>
       <c r="W13">
         <v>1.24</v>
@@ -2464,7 +2464,7 @@
         <v>1.04</v>
       </c>
       <c r="Z13">
-        <v>6.9</v>
+        <v>6.85</v>
       </c>
       <c r="AA13">
         <v>1.28</v>
@@ -2501,7 +2501,7 @@
         <v>1.1</v>
       </c>
       <c r="AK13">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -638,16 +638,16 @@
         <v>2.87</v>
       </c>
       <c r="O2">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P2">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="Q2">
         <v>3.45</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S2">
         <v>1.35</v>
@@ -656,28 +656,28 @@
         <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="V2">
         <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AA2">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB2">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC2">
         <v>3.24</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O3">
+        <v>3.6</v>
+      </c>
+      <c r="P3">
         <v>3.55</v>
-      </c>
-      <c r="P3">
-        <v>3.6</v>
       </c>
       <c r="Q3">
         <v>2.46</v>
@@ -816,7 +816,7 @@
         <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U3">
         <v>2.62</v>
@@ -840,7 +840,7 @@
         <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AC3">
         <v>2.94</v>
@@ -852,10 +852,10 @@
         <v>1.12</v>
       </c>
       <c r="AF3">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
         <v>1.73</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="O4">
-        <v>3.76</v>
+        <v>3.86</v>
       </c>
       <c r="P4">
-        <v>5.35</v>
+        <v>4.7</v>
       </c>
       <c r="Q4">
+        <v>2.15</v>
+      </c>
+      <c r="R4">
         <v>2.2</v>
       </c>
-      <c r="R4">
-        <v>2.1</v>
-      </c>
       <c r="S4">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="T4">
         <v>2.75</v>
       </c>
       <c r="U4">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W4">
         <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
         <v>1.33</v>
       </c>
       <c r="Z4">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AA4">
         <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
         <v>3.55</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG4">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK4">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>1.85</v>
       </c>
       <c r="Q5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R5">
         <v>2.3</v>
@@ -1151,37 +1151,37 @@
         <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB5">
         <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
         <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="R6">
         <v>2.25</v>
@@ -1308,25 +1308,25 @@
         <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
         <v>3.8</v>
       </c>
       <c r="AA6">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB6">
         <v>2.04</v>
@@ -1338,10 +1338,10 @@
         <v>1.36</v>
       </c>
       <c r="AE6">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
         <v>2.2</v>
@@ -1360,7 +1360,7 @@
         <v>1.7</v>
       </c>
       <c r="AK6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O7">
         <v>3.7</v>
       </c>
       <c r="P7">
-        <v>3.22</v>
+        <v>2.95</v>
       </c>
       <c r="Q7">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="R7">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S7">
         <v>1.25</v>
@@ -1471,28 +1471,28 @@
         <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W7">
         <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z7">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA7">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB7">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC7">
         <v>2.43</v>
@@ -1501,13 +1501,13 @@
         <v>1.47</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF7">
         <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK7">
         <v>1.7</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.17</v>
+        <v>1.55</v>
       </c>
       <c r="O8">
-        <v>7.75</v>
+        <v>4.33</v>
       </c>
       <c r="P8">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="Q8">
-        <v>1.55</v>
+        <v>1.99</v>
       </c>
       <c r="R8">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="S8">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="U8">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
+        <v>1.1</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.2</v>
+      </c>
+      <c r="Z8">
+        <v>4.33</v>
+      </c>
+      <c r="AA8">
+        <v>1.67</v>
+      </c>
+      <c r="AB8">
+        <v>2.1</v>
+      </c>
+      <c r="AC8">
+        <v>2.45</v>
+      </c>
+      <c r="AD8">
+        <v>1.48</v>
+      </c>
+      <c r="AE8">
         <v>1.13</v>
       </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.13</v>
-      </c>
-      <c r="Z8">
-        <v>4.93</v>
-      </c>
-      <c r="AA8">
-        <v>1.57</v>
-      </c>
-      <c r="AB8">
-        <v>2.35</v>
-      </c>
-      <c r="AC8">
-        <v>2.38</v>
-      </c>
-      <c r="AD8">
-        <v>1.59</v>
-      </c>
-      <c r="AE8">
-        <v>1.18</v>
-      </c>
       <c r="AF8">
-        <v>2.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK8">
-        <v>5</v>
+        <v>2.27</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.55</v>
+        <v>1.17</v>
       </c>
       <c r="O9">
-        <v>4.33</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>5.5</v>
+        <v>15</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="R9">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="U9">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
+        <v>1.14</v>
+      </c>
+      <c r="Z9">
+        <v>5</v>
+      </c>
+      <c r="AA9">
+        <v>1.57</v>
+      </c>
+      <c r="AB9">
+        <v>2.35</v>
+      </c>
+      <c r="AC9">
+        <v>2.45</v>
+      </c>
+      <c r="AD9">
+        <v>1.53</v>
+      </c>
+      <c r="AE9">
         <v>1.2</v>
       </c>
-      <c r="Z9">
-        <v>4.1</v>
-      </c>
-      <c r="AA9">
-        <v>1.65</v>
-      </c>
-      <c r="AB9">
-        <v>2.08</v>
-      </c>
-      <c r="AC9">
-        <v>2.65</v>
-      </c>
-      <c r="AD9">
-        <v>1.48</v>
-      </c>
-      <c r="AE9">
-        <v>1.13</v>
-      </c>
       <c r="AF9">
-        <v>1.75</v>
+        <v>2.38</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AK9">
-        <v>2.43</v>
+        <v>5.2</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="O2">
         <v>3.32</v>
       </c>
       <c r="P2">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="Q2">
         <v>3.45</v>
@@ -656,22 +656,22 @@
         <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="V2">
         <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AA2">
         <v>1.95</v>
@@ -680,19 +680,19 @@
         <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="AD2">
         <v>1.31</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P3">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="Q3">
         <v>2.46</v>
@@ -813,10 +813,10 @@
         <v>2.23</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T3">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U3">
         <v>2.62</v>
@@ -855,7 +855,7 @@
         <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
         <v>1.73</v>
@@ -967,58 +967,58 @@
         <v>3.86</v>
       </c>
       <c r="P4">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="Q4">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="R4">
         <v>2.2</v>
       </c>
       <c r="S4">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U4">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="V4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
         <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z4">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF4">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="O5">
-        <v>3.8</v>
+        <v>3.51</v>
       </c>
       <c r="P5">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q5">
         <v>4.2</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S5">
         <v>1.32</v>
@@ -1145,10 +1145,10 @@
         <v>3.1</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
         <v>1.09</v>
@@ -1160,13 +1160,13 @@
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AA5">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AB5">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC5">
         <v>2.8</v>
@@ -1175,13 +1175,13 @@
         <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
         <v>1.65</v>
       </c>
       <c r="AG5">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
         <v>1.2</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="O6">
         <v>3.6</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q6">
         <v>3.5</v>
       </c>
       <c r="R6">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S6">
         <v>1.32</v>
@@ -1308,19 +1308,19 @@
         <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W6">
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
         <v>3.8</v>
@@ -1329,10 +1329,10 @@
         <v>1.72</v>
       </c>
       <c r="AB6">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AC6">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AD6">
         <v>1.36</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="Q7">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="R7">
         <v>2.4</v>
@@ -1471,28 +1471,28 @@
         <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="V7">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W7">
         <v>1.13</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB7">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AC7">
         <v>2.43</v>
@@ -1501,13 +1501,13 @@
         <v>1.47</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
         <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O8">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="P8">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q8">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R8">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S8">
         <v>1.29</v>
@@ -1637,13 +1637,13 @@
         <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W8">
         <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
         <v>1.2</v>
@@ -1661,10 +1661,10 @@
         <v>2.45</v>
       </c>
       <c r="AD8">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
         <v>1.7</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK8">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O9">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="P9">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q9">
         <v>1.53</v>
@@ -1800,7 +1800,7 @@
         <v>2.32</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W9">
         <v>1.11</v>
@@ -1818,19 +1818,19 @@
         <v>1.57</v>
       </c>
       <c r="AB9">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AC9">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AD9">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE9">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF9">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG9">
         <v>1.45</v>
@@ -1849,7 +1849,7 @@
         <v>1.08</v>
       </c>
       <c r="AK9">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.17</v>
+        <v>3.51</v>
       </c>
       <c r="O10">
+        <v>4.1</v>
+      </c>
+      <c r="P10">
+        <v>1.53</v>
+      </c>
+      <c r="Q10">
         <v>3.9</v>
-      </c>
-      <c r="P10">
-        <v>1.67</v>
-      </c>
-      <c r="Q10">
-        <v>4.26</v>
       </c>
       <c r="R10">
         <v>2.75</v>
       </c>
       <c r="S10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="U10">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="V10">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="W10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z10">
-        <v>7.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB10">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AC10">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AD10">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AE10">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AF10">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG10">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P11">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="R11">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="S11">
         <v>1.14</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="U11">
         <v>1.8</v>
@@ -2141,10 +2141,10 @@
         <v>8.1</v>
       </c>
       <c r="AA11">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AB11">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC11">
         <v>1.7</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AK11">
         <v>1.73</v>
@@ -2265,25 +2265,25 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="O12">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T12">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="U12">
         <v>2.17</v>
@@ -2292,16 +2292,16 @@
         <v>1.61</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA12">
         <v>1.53</v>
@@ -2319,10 +2319,10 @@
         <v>1.21</v>
       </c>
       <c r="AF12">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG12">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O13">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>7.47</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>1.74</v>
@@ -2449,10 +2449,10 @@
         <v>5</v>
       </c>
       <c r="U13">
+        <v>1.87</v>
+      </c>
+      <c r="V13">
         <v>1.8</v>
-      </c>
-      <c r="V13">
-        <v>1.91</v>
       </c>
       <c r="W13">
         <v>1.24</v>
@@ -2461,22 +2461,22 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z13">
-        <v>6.85</v>
+        <v>7.5</v>
       </c>
       <c r="AA13">
         <v>1.28</v>
       </c>
       <c r="AB13">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="AC13">
         <v>1.8</v>
       </c>
       <c r="AD13">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AE13">
         <v>1.36</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.32</v>
+        <v>1.5</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="P6">
-        <v>2.15</v>
+        <v>5.8</v>
       </c>
       <c r="Q6">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="R6">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S6">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U6">
         <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA6">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE6">
+        <v>1.15</v>
+      </c>
+      <c r="AF6">
+        <v>1.7</v>
+      </c>
+      <c r="AG6">
+        <v>2.05</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.13</v>
       </c>
-      <c r="AF6">
-        <v>1.62</v>
-      </c>
-      <c r="AG6">
-        <v>2.2</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.29</v>
-      </c>
       <c r="AK6">
-        <v>1.34</v>
+        <v>2.43</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.97</v>
+        <v>3.32</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="Q7">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="R7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W7">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA7">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AB7">
-        <v>2.31</v>
+        <v>1.95</v>
       </c>
       <c r="AC7">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AD7">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.29</v>
       </c>
       <c r="AK7">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="O8">
-        <v>4.15</v>
+        <v>3.75</v>
       </c>
       <c r="P8">
-        <v>5.8</v>
+        <v>2.93</v>
       </c>
       <c r="Q8">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="R8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S8">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z8">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AA8">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AC8">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AD8">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE8">
         <v>1.15</v>
       </c>
       <c r="AF8">
+        <v>1.5</v>
+      </c>
+      <c r="AG8">
+        <v>2.35</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.29</v>
+      </c>
+      <c r="AK8">
         <v>1.7</v>
-      </c>
-      <c r="AG8">
-        <v>2.05</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.13</v>
-      </c>
-      <c r="AK8">
-        <v>2.43</v>
       </c>
       <c r="AL8">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="O2">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R2">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
         <v>2.75</v>
@@ -659,7 +659,7 @@
         <v>2.66</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W2">
         <v>1.08</v>
@@ -671,7 +671,7 @@
         <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
         <v>1.95</v>
@@ -680,19 +680,19 @@
         <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG2">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="O3">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P3">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
         <v>2.23</v>
       </c>
       <c r="S3">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U3">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X3">
         <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z3">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AA3">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB3">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AC3">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AD3">
         <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O4">
-        <v>3.86</v>
+        <v>3.65</v>
       </c>
       <c r="P4">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="Q4">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T4">
+        <v>2.59</v>
+      </c>
+      <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4">
+        <v>1.33</v>
+      </c>
+      <c r="W4">
+        <v>1.04</v>
+      </c>
+      <c r="X4">
+        <v>1.04</v>
+      </c>
+      <c r="Y4">
+        <v>1.36</v>
+      </c>
+      <c r="Z4">
         <v>2.9</v>
-      </c>
-      <c r="U4">
-        <v>2.88</v>
-      </c>
-      <c r="V4">
-        <v>1.4</v>
-      </c>
-      <c r="W4">
-        <v>1.05</v>
-      </c>
-      <c r="X4">
-        <v>1.05</v>
-      </c>
-      <c r="Y4">
-        <v>1.32</v>
-      </c>
-      <c r="Z4">
-        <v>3.4</v>
       </c>
       <c r="AA4">
         <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC4">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG4">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK4">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="O5">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="P5">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U5">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
         <v>1.03</v>
@@ -1160,28 +1160,28 @@
         <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA5">
         <v>1.77</v>
       </c>
       <c r="AB5">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC5">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AD5">
         <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.84</v>
       </c>
       <c r="AK5">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1293,31 +1293,31 @@
         <v>4.15</v>
       </c>
       <c r="P6">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V6">
         <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
@@ -1326,25 +1326,25 @@
         <v>4.33</v>
       </c>
       <c r="AA6">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AC6">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AD6">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE6">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
         <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.32</v>
+        <v>3.19</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q7">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="R7">
         <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z7">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AA7">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AB7">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC7">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="AD7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
         <v>1.62</v>
       </c>
       <c r="AG7">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="O8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="Q8">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="S8">
         <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="V8">
         <v>1.54</v>
@@ -1643,19 +1643,19 @@
         <v>1.13</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
         <v>4.6</v>
       </c>
       <c r="AA8">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB8">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="AC8">
         <v>2.43</v>
@@ -1664,13 +1664,13 @@
         <v>1.47</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG8">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AK8">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="O9">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="P9">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="Q9">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R9">
         <v>2.7</v>
@@ -1794,40 +1794,40 @@
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="U9">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V9">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA9">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB9">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AD9">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE9">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
         <v>2.4</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK9">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="O10">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="P10">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="Q10">
         <v>3.9</v>
@@ -1957,13 +1957,13 @@
         <v>1.15</v>
       </c>
       <c r="T10">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="U10">
         <v>1.89</v>
       </c>
       <c r="V10">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="W10">
         <v>1.2</v>
@@ -1972,31 +1972,31 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z10">
-        <v>4.1</v>
+        <v>6.95</v>
       </c>
       <c r="AA10">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB10">
         <v>3.25</v>
       </c>
       <c r="AC10">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE10">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AF10">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG10">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.19</v>
+        <v>1.18</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="P7">
-        <v>2.08</v>
+        <v>15</v>
       </c>
       <c r="Q7">
-        <v>3.78</v>
+        <v>1.49</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>2.87</v>
+        <v>3.14</v>
       </c>
       <c r="U7">
+        <v>2.25</v>
+      </c>
+      <c r="V7">
+        <v>1.57</v>
+      </c>
+      <c r="W7">
+        <v>1.12</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>1.15</v>
+      </c>
+      <c r="Z7">
+        <v>4.5</v>
+      </c>
+      <c r="AA7">
+        <v>1.53</v>
+      </c>
+      <c r="AB7">
+        <v>2.25</v>
+      </c>
+      <c r="AC7">
+        <v>2.45</v>
+      </c>
+      <c r="AD7">
+        <v>1.53</v>
+      </c>
+      <c r="AE7">
+        <v>1.18</v>
+      </c>
+      <c r="AF7">
         <v>2.4</v>
       </c>
-      <c r="V7">
-        <v>1.48</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.04</v>
-      </c>
-      <c r="Y7">
-        <v>1.22</v>
-      </c>
-      <c r="Z7">
-        <v>3.85</v>
-      </c>
-      <c r="AA7">
-        <v>1.67</v>
-      </c>
-      <c r="AB7">
-        <v>2.02</v>
-      </c>
-      <c r="AC7">
-        <v>2.65</v>
-      </c>
-      <c r="AD7">
-        <v>1.4</v>
-      </c>
-      <c r="AE7">
-        <v>1.14</v>
-      </c>
-      <c r="AF7">
-        <v>1.62</v>
-      </c>
       <c r="AG7">
-        <v>2.18</v>
+        <v>1.45</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AK7">
-        <v>1.22</v>
+        <v>5</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.2</v>
+        <v>3.19</v>
       </c>
       <c r="O8">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
+        <v>2.08</v>
+      </c>
+      <c r="Q8">
+        <v>3.78</v>
+      </c>
+      <c r="R8">
+        <v>2.3</v>
+      </c>
+      <c r="S8">
+        <v>1.3</v>
+      </c>
+      <c r="T8">
+        <v>2.87</v>
+      </c>
+      <c r="U8">
+        <v>2.4</v>
+      </c>
+      <c r="V8">
+        <v>1.48</v>
+      </c>
+      <c r="W8">
+        <v>1.11</v>
+      </c>
+      <c r="X8">
+        <v>1.04</v>
+      </c>
+      <c r="Y8">
+        <v>1.22</v>
+      </c>
+      <c r="Z8">
+        <v>3.85</v>
+      </c>
+      <c r="AA8">
+        <v>1.67</v>
+      </c>
+      <c r="AB8">
+        <v>2.02</v>
+      </c>
+      <c r="AC8">
         <v>2.65</v>
       </c>
-      <c r="Q8">
-        <v>2.6</v>
-      </c>
-      <c r="R8">
-        <v>2.19</v>
-      </c>
-      <c r="S8">
+      <c r="AD8">
+        <v>1.4</v>
+      </c>
+      <c r="AE8">
+        <v>1.14</v>
+      </c>
+      <c r="AF8">
+        <v>1.62</v>
+      </c>
+      <c r="AG8">
+        <v>2.18</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
         <v>1.25</v>
       </c>
-      <c r="T8">
-        <v>3.3</v>
-      </c>
-      <c r="U8">
-        <v>2.39</v>
-      </c>
-      <c r="V8">
-        <v>1.54</v>
-      </c>
-      <c r="W8">
-        <v>1.13</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>1.2</v>
-      </c>
-      <c r="Z8">
-        <v>4.6</v>
-      </c>
-      <c r="AA8">
-        <v>1.58</v>
-      </c>
-      <c r="AB8">
-        <v>2.18</v>
-      </c>
-      <c r="AC8">
-        <v>2.43</v>
-      </c>
-      <c r="AD8">
-        <v>1.47</v>
-      </c>
-      <c r="AE8">
-        <v>1.18</v>
-      </c>
-      <c r="AF8">
-        <v>1.53</v>
-      </c>
-      <c r="AG8">
-        <v>2.4</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.38</v>
-      </c>
       <c r="AK8">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="O9">
-        <v>7.5</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>15</v>
+        <v>2.65</v>
       </c>
       <c r="Q9">
-        <v>1.49</v>
+        <v>2.6</v>
       </c>
       <c r="R9">
-        <v>2.7</v>
+        <v>2.19</v>
       </c>
       <c r="S9">
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="U9">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA9">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC9">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AD9">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AE9">
         <v>1.18</v>
       </c>
       <c r="AF9">
+        <v>1.53</v>
+      </c>
+      <c r="AG9">
         <v>2.4</v>
       </c>
-      <c r="AG9">
-        <v>1.45</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="AK9">
-        <v>5</v>
+        <v>1.68</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>2.87</v>
       </c>
       <c r="Q11">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="R11">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="S11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T11">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="U11">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="V11">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="W11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z11">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="AA11">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB11">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AC11">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD11">
         <v>2.05</v>
       </c>
       <c r="AE11">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF11">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AG11">
-        <v>3.58</v>
+        <v>3.43</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AK11">
         <v>1.73</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O12">
         <v>3.5</v>
@@ -2274,55 +2274,55 @@
         <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R12">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="U12">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W12">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="AA12">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB12">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC12">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD12">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE12">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG12">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="O13">
         <v>5</v>
@@ -2437,55 +2437,55 @@
         <v>6</v>
       </c>
       <c r="Q13">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R13">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="S13">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="U13">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="V13">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W13">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z13">
         <v>7.5</v>
       </c>
       <c r="AA13">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB13">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="AC13">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD13">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AE13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG13">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK13">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.55</v>
+        <v>3.9</v>
       </c>
       <c r="O4">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P4">
-        <v>5.3</v>
+        <v>1.9</v>
       </c>
       <c r="Q4">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="T4">
-        <v>2.59</v>
+        <v>3.15</v>
       </c>
       <c r="U4">
-        <v>3</v>
+        <v>2.47</v>
       </c>
       <c r="V4">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AB4">
+        <v>2.05</v>
+      </c>
+      <c r="AC4">
+        <v>2.66</v>
+      </c>
+      <c r="AD4">
+        <v>1.4</v>
+      </c>
+      <c r="AE4">
+        <v>1.13</v>
+      </c>
+      <c r="AF4">
         <v>1.67</v>
       </c>
-      <c r="AC4">
-        <v>3.85</v>
-      </c>
-      <c r="AD4">
-        <v>1.21</v>
-      </c>
-      <c r="AE4">
-        <v>1.06</v>
-      </c>
-      <c r="AF4">
-        <v>2</v>
-      </c>
       <c r="AG4">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.13</v>
+        <v>1.84</v>
       </c>
       <c r="AK4">
-        <v>2.24</v>
+        <v>1.24</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.9</v>
+        <v>1.55</v>
       </c>
       <c r="O5">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P5">
-        <v>1.9</v>
+        <v>5.3</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="T5">
-        <v>3.15</v>
+        <v>2.59</v>
       </c>
       <c r="U5">
-        <v>2.47</v>
+        <v>3</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA5">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AB5">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AE5">
+        <v>1.06</v>
+      </c>
+      <c r="AF5">
+        <v>2</v>
+      </c>
+      <c r="AG5">
+        <v>1.67</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.13</v>
       </c>
-      <c r="AF5">
-        <v>1.67</v>
-      </c>
-      <c r="AG5">
-        <v>2.02</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.84</v>
-      </c>
       <c r="AK5">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="O10">
         <v>3.85</v>
       </c>
       <c r="P10">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="Q10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="S10">
         <v>1.15</v>
@@ -1960,7 +1960,7 @@
         <v>4.35</v>
       </c>
       <c r="U10">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V10">
         <v>1.88</v>
@@ -1984,7 +1984,7 @@
         <v>3.25</v>
       </c>
       <c r="AC10">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AD10">
         <v>1.93</v>
@@ -1996,7 +1996,7 @@
         <v>1.34</v>
       </c>
       <c r="AG10">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK10">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,65 +1613,65 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.19</v>
+        <v>2.2</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="Q8">
-        <v>3.78</v>
+        <v>2.6</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
+        <v>2.39</v>
+      </c>
+      <c r="V8">
+        <v>1.54</v>
+      </c>
+      <c r="W8">
+        <v>1.13</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>1.2</v>
+      </c>
+      <c r="Z8">
+        <v>4.6</v>
+      </c>
+      <c r="AA8">
+        <v>1.58</v>
+      </c>
+      <c r="AB8">
+        <v>2.18</v>
+      </c>
+      <c r="AC8">
+        <v>2.43</v>
+      </c>
+      <c r="AD8">
+        <v>1.47</v>
+      </c>
+      <c r="AE8">
+        <v>1.18</v>
+      </c>
+      <c r="AF8">
+        <v>1.53</v>
+      </c>
+      <c r="AG8">
         <v>2.4</v>
       </c>
-      <c r="V8">
-        <v>1.48</v>
-      </c>
-      <c r="W8">
-        <v>1.11</v>
-      </c>
-      <c r="X8">
-        <v>1.04</v>
-      </c>
-      <c r="Y8">
-        <v>1.22</v>
-      </c>
-      <c r="Z8">
-        <v>3.85</v>
-      </c>
-      <c r="AA8">
-        <v>1.67</v>
-      </c>
-      <c r="AB8">
-        <v>2.02</v>
-      </c>
-      <c r="AC8">
-        <v>2.65</v>
-      </c>
-      <c r="AD8">
-        <v>1.4</v>
-      </c>
-      <c r="AE8">
-        <v>1.14</v>
-      </c>
-      <c r="AF8">
-        <v>1.62</v>
-      </c>
-      <c r="AG8">
-        <v>2.18</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK8">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.2</v>
+        <v>3.19</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
+        <v>2.08</v>
+      </c>
+      <c r="Q9">
+        <v>3.78</v>
+      </c>
+      <c r="R9">
+        <v>2.3</v>
+      </c>
+      <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
+        <v>2.87</v>
+      </c>
+      <c r="U9">
+        <v>2.4</v>
+      </c>
+      <c r="V9">
+        <v>1.48</v>
+      </c>
+      <c r="W9">
+        <v>1.11</v>
+      </c>
+      <c r="X9">
+        <v>1.04</v>
+      </c>
+      <c r="Y9">
+        <v>1.22</v>
+      </c>
+      <c r="Z9">
+        <v>3.85</v>
+      </c>
+      <c r="AA9">
+        <v>1.67</v>
+      </c>
+      <c r="AB9">
+        <v>2.02</v>
+      </c>
+      <c r="AC9">
         <v>2.65</v>
       </c>
-      <c r="Q9">
-        <v>2.6</v>
-      </c>
-      <c r="R9">
-        <v>2.19</v>
-      </c>
-      <c r="S9">
+      <c r="AD9">
+        <v>1.4</v>
+      </c>
+      <c r="AE9">
+        <v>1.14</v>
+      </c>
+      <c r="AF9">
+        <v>1.62</v>
+      </c>
+      <c r="AG9">
+        <v>2.18</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.25</v>
       </c>
-      <c r="T9">
-        <v>3.3</v>
-      </c>
-      <c r="U9">
-        <v>2.39</v>
-      </c>
-      <c r="V9">
-        <v>1.54</v>
-      </c>
-      <c r="W9">
-        <v>1.13</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>1.2</v>
-      </c>
-      <c r="Z9">
-        <v>4.6</v>
-      </c>
-      <c r="AA9">
-        <v>1.58</v>
-      </c>
-      <c r="AB9">
-        <v>2.18</v>
-      </c>
-      <c r="AC9">
-        <v>2.43</v>
-      </c>
-      <c r="AD9">
-        <v>1.47</v>
-      </c>
-      <c r="AE9">
-        <v>1.18</v>
-      </c>
-      <c r="AF9">
-        <v>1.53</v>
-      </c>
-      <c r="AG9">
-        <v>2.4</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.38</v>
-      </c>
       <c r="AK9">
-        <v>1.68</v>
+        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -656,13 +656,13 @@
         <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="V2">
         <v>1.39</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.03</v>
@@ -671,7 +671,7 @@
         <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA2">
         <v>1.95</v>
@@ -680,7 +680,7 @@
         <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="AD2">
         <v>1.32</v>
@@ -708,7 +708,7 @@
         <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>3.32</v>
+        <v>2.99</v>
       </c>
       <c r="Q3">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R3">
         <v>2.23</v>
@@ -819,43 +819,43 @@
         <v>3.1</v>
       </c>
       <c r="U3">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA3">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB3">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AC3">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AD3">
         <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.19</v>
       </c>
       <c r="AK3">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
+        <v>4.1</v>
+      </c>
+      <c r="O4">
         <v>3.9</v>
       </c>
-      <c r="O4">
-        <v>3.55</v>
-      </c>
       <c r="P4">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
         <v>1.31</v>
@@ -988,10 +988,10 @@
         <v>1.48</v>
       </c>
       <c r="W4">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.22</v>
@@ -1006,35 +1006,35 @@
         <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AD4">
         <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG4">
+        <v>2.15</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>2.02</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.84</v>
-      </c>
       <c r="AK4">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O5">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P5">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="Q5">
         <v>2.2</v>
@@ -1139,10 +1139,10 @@
         <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T5">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -1151,13 +1151,13 @@
         <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z5">
         <v>2.9</v>
@@ -1166,22 +1166,22 @@
         <v>2.1</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AD5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
         <v>2</v>
       </c>
       <c r="AG5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.13</v>
       </c>
       <c r="AK5">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1293,43 +1293,43 @@
         <v>4.15</v>
       </c>
       <c r="P6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="Q6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
         <v>3.16</v>
       </c>
       <c r="U6">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V6">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AA6">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AC6">
         <v>2.55</v>
@@ -1338,13 +1338,13 @@
         <v>1.48</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
         <v>2.38</v>
@@ -1453,31 +1453,31 @@
         <v>1.18</v>
       </c>
       <c r="O7">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q7">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="R7">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
         <v>3.14</v>
       </c>
       <c r="U7">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1489,26 +1489,26 @@
         <v>4.5</v>
       </c>
       <c r="AA7">
+        <v>1.48</v>
+      </c>
+      <c r="AB7">
+        <v>2.31</v>
+      </c>
+      <c r="AC7">
+        <v>2.35</v>
+      </c>
+      <c r="AD7">
+        <v>1.57</v>
+      </c>
+      <c r="AE7">
+        <v>1.2</v>
+      </c>
+      <c r="AF7">
+        <v>2.35</v>
+      </c>
+      <c r="AG7">
         <v>1.53</v>
       </c>
-      <c r="AB7">
-        <v>2.25</v>
-      </c>
-      <c r="AC7">
-        <v>2.45</v>
-      </c>
-      <c r="AD7">
-        <v>1.53</v>
-      </c>
-      <c r="AE7">
-        <v>1.18</v>
-      </c>
-      <c r="AF7">
-        <v>2.4</v>
-      </c>
-      <c r="AG7">
-        <v>1.45</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK7">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1616,16 +1616,16 @@
         <v>2.2</v>
       </c>
       <c r="O8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="P8">
         <v>2.65</v>
       </c>
       <c r="Q8">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R8">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="S8">
         <v>1.25</v>
@@ -1643,31 +1643,31 @@
         <v>1.13</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
         <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB8">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AC8">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AD8">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG8">
         <v>2.4</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="P9">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q9">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="R9">
         <v>2.3</v>
@@ -1794,13 +1794,13 @@
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V9">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W9">
         <v>1.11</v>
@@ -1812,25 +1812,25 @@
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AC9">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="AD9">
         <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG9">
         <v>2.18</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -644,10 +644,10 @@
         <v>2.5</v>
       </c>
       <c r="Q2">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R2">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S2">
         <v>1.36</v>
@@ -656,10 +656,10 @@
         <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W2">
         <v>1.05</v>
@@ -671,7 +671,7 @@
         <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA2">
         <v>1.95</v>
@@ -680,10 +680,10 @@
         <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.27</v>
+        <v>3.12</v>
       </c>
       <c r="AD2">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE2">
         <v>1.1</v>
@@ -804,7 +804,7 @@
         <v>3.5</v>
       </c>
       <c r="P3">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="Q3">
         <v>2.51</v>
@@ -819,31 +819,31 @@
         <v>3.1</v>
       </c>
       <c r="U3">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
         <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="AA3">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB3">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC3">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AD3">
         <v>1.31</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>1.8</v>
       </c>
       <c r="Q4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R4">
         <v>2.3</v>
@@ -1000,13 +1000,13 @@
         <v>3.9</v>
       </c>
       <c r="AA4">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB4">
         <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD4">
         <v>1.4</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O5">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="P5">
         <v>5.55</v>
       </c>
       <c r="Q5">
+        <v>2.1</v>
+      </c>
+      <c r="R5">
         <v>2.2</v>
-      </c>
-      <c r="R5">
-        <v>2.1</v>
       </c>
       <c r="S5">
         <v>1.42</v>
       </c>
       <c r="T5">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U5">
         <v>3</v>
@@ -1154,7 +1154,7 @@
         <v>1.07</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
         <v>1.37</v>
@@ -1172,10 +1172,10 @@
         <v>4</v>
       </c>
       <c r="AD5">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
         <v>2</v>
@@ -1293,22 +1293,22 @@
         <v>4.15</v>
       </c>
       <c r="P6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="R6">
         <v>2.35</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
         <v>3.16</v>
       </c>
       <c r="U6">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="V6">
         <v>1.5</v>
@@ -1317,7 +1317,7 @@
         <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
@@ -1332,19 +1332,19 @@
         <v>2.15</v>
       </c>
       <c r="AC6">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD6">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
         <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,31 +1450,31 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.18</v>
+        <v>2.08</v>
       </c>
       <c r="O7">
-        <v>8.300000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="P7">
-        <v>18</v>
+        <v>2.65</v>
       </c>
       <c r="Q7">
-        <v>1.44</v>
+        <v>2.62</v>
       </c>
       <c r="R7">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="S7">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="V7">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="W7">
         <v>1.14</v>
@@ -1483,31 +1483,31 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.5</v>
+        <v>4.79</v>
       </c>
       <c r="AA7">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AC7">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AD7">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE7">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF7">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="AK7">
-        <v>5.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="Q8">
+        <v>3.78</v>
+      </c>
+      <c r="R8">
+        <v>2.3</v>
+      </c>
+      <c r="S8">
+        <v>1.3</v>
+      </c>
+      <c r="T8">
+        <v>3.1</v>
+      </c>
+      <c r="U8">
         <v>2.45</v>
       </c>
-      <c r="R8">
-        <v>2.24</v>
-      </c>
-      <c r="S8">
-        <v>1.25</v>
-      </c>
-      <c r="T8">
-        <v>3.3</v>
-      </c>
-      <c r="U8">
-        <v>2.39</v>
-      </c>
       <c r="V8">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA8">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AB8">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="AD8">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AG8">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.2</v>
+        <v>1.15</v>
       </c>
       <c r="O9">
-        <v>3.49</v>
+        <v>7.75</v>
       </c>
       <c r="P9">
-        <v>2.04</v>
+        <v>15</v>
       </c>
       <c r="Q9">
-        <v>3.82</v>
+        <v>1.45</v>
       </c>
       <c r="R9">
+        <v>2.76</v>
+      </c>
+      <c r="S9">
+        <v>1.21</v>
+      </c>
+      <c r="T9">
+        <v>3.14</v>
+      </c>
+      <c r="U9">
+        <v>2.2</v>
+      </c>
+      <c r="V9">
+        <v>1.62</v>
+      </c>
+      <c r="W9">
+        <v>1.12</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.17</v>
+      </c>
+      <c r="Z9">
+        <v>5</v>
+      </c>
+      <c r="AA9">
+        <v>1.53</v>
+      </c>
+      <c r="AB9">
+        <v>2.37</v>
+      </c>
+      <c r="AC9">
         <v>2.3</v>
       </c>
-      <c r="S9">
-        <v>1.3</v>
-      </c>
-      <c r="T9">
-        <v>3.1</v>
-      </c>
-      <c r="U9">
-        <v>2.45</v>
-      </c>
-      <c r="V9">
-        <v>1.47</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.04</v>
-      </c>
-      <c r="Y9">
-        <v>1.22</v>
-      </c>
-      <c r="Z9">
-        <v>3.8</v>
-      </c>
-      <c r="AA9">
-        <v>1.7</v>
-      </c>
-      <c r="AB9">
-        <v>1.98</v>
-      </c>
-      <c r="AC9">
-        <v>2.9</v>
-      </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF9">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="AG9">
-        <v>2.18</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AK9">
-        <v>1.22</v>
+        <v>6</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.51</v>
+        <v>3.8</v>
       </c>
       <c r="O10">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P10">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R10">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="S10">
         <v>1.15</v>
@@ -1960,10 +1960,10 @@
         <v>4.35</v>
       </c>
       <c r="U10">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V10">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="W10">
         <v>1.2</v>
@@ -1972,31 +1972,31 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z10">
         <v>6.95</v>
       </c>
       <c r="AA10">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB10">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AC10">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AD10">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AE10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF10">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG10">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.06</v>
       </c>
       <c r="AK10">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="O11">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="P11">
-        <v>2.87</v>
+        <v>3.32</v>
       </c>
       <c r="Q11">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
-        <v>2.46</v>
+        <v>2.61</v>
       </c>
       <c r="S11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="U11">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="V11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AA11">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB11">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AC11">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="AD11">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AE11">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AF11">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AG11">
-        <v>3.43</v>
+        <v>3.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="P12">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q12">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
         <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U12">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V12">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W12">
         <v>1.15</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.1</v>
       </c>
       <c r="Z12">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA12">
         <v>1.5</v>
       </c>
       <c r="AB12">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AC12">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AD12">
         <v>1.58</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AF12">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG12">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AK12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="O13">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="P13">
-        <v>6</v>
+        <v>7.65</v>
       </c>
       <c r="Q13">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R13">
         <v>2.8</v>
@@ -2446,13 +2446,13 @@
         <v>1.16</v>
       </c>
       <c r="T13">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="U13">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="V13">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W13">
         <v>1.22</v>
@@ -2461,31 +2461,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z13">
         <v>7.5</v>
       </c>
       <c r="AA13">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="AC13">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AD13">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AE13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF13">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK13">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
         <v>2.5</v>
@@ -647,7 +647,7 @@
         <v>3.25</v>
       </c>
       <c r="R2">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="S2">
         <v>1.36</v>
@@ -656,22 +656,22 @@
         <v>2.75</v>
       </c>
       <c r="U2">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W2">
+        <v>1.08</v>
+      </c>
+      <c r="X2">
         <v>1.05</v>
-      </c>
-      <c r="X2">
-        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.3</v>
       </c>
       <c r="Z2">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="AA2">
         <v>1.95</v>
@@ -680,7 +680,7 @@
         <v>1.73</v>
       </c>
       <c r="AC2">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="AD2">
         <v>1.3</v>
@@ -801,16 +801,16 @@
         <v>2.1</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="R3">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S3">
         <v>1.33</v>
@@ -819,43 +819,43 @@
         <v>3.1</v>
       </c>
       <c r="U3">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="AA3">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB3">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AD3">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF3">
         <v>1.67</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,16 +961,16 @@
         </is>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>3.9</v>
+        <v>3.51</v>
       </c>
       <c r="P4">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q4">
-        <v>4.6</v>
+        <v>3.86</v>
       </c>
       <c r="R4">
         <v>2.3</v>
@@ -982,10 +982,10 @@
         <v>3.15</v>
       </c>
       <c r="U4">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V4">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
         <v>1.11</v>
@@ -997,16 +997,16 @@
         <v>1.22</v>
       </c>
       <c r="Z4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA4">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AD4">
         <v>1.4</v>
@@ -1034,7 +1034,7 @@
         <v>2.02</v>
       </c>
       <c r="AK4">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O5">
         <v>3.65</v>
       </c>
       <c r="P5">
-        <v>5.55</v>
+        <v>4.8</v>
       </c>
       <c r="Q5">
         <v>2.1</v>
       </c>
       <c r="R5">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="T5">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z5">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AA5">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AB5">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AC5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
         <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK5">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="O6">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P6">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Q6">
         <v>2.03</v>
@@ -1308,40 +1308,40 @@
         <v>3.16</v>
       </c>
       <c r="U6">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V6">
         <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB6">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
         <v>2.56</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE6">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF6">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG6">
         <v>2</v>
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="Q7">
         <v>2.62</v>
       </c>
       <c r="R7">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
         <v>3.5</v>
       </c>
       <c r="U7">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="V7">
         <v>1.54</v>
@@ -1480,31 +1480,31 @@
         <v>1.14</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z7">
-        <v>4.79</v>
+        <v>4.7</v>
       </c>
       <c r="AA7">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB7">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AC7">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="AD7">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AE7">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG7">
         <v>2.4</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK7">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q8">
-        <v>3.78</v>
+        <v>3.88</v>
       </c>
       <c r="R8">
         <v>2.3</v>
@@ -1631,7 +1631,7 @@
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U8">
         <v>2.45</v>
@@ -1649,28 +1649,28 @@
         <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.9</v>
+        <v>4.13</v>
       </c>
       <c r="AA8">
         <v>1.71</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD8">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
         <v>1.3</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="O9">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>15</v>
+        <v>14.78</v>
       </c>
       <c r="Q9">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R9">
-        <v>2.76</v>
+        <v>3.06</v>
       </c>
       <c r="S9">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V9">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA9">
+        <v>1.6</v>
+      </c>
+      <c r="AB9">
+        <v>2.4</v>
+      </c>
+      <c r="AC9">
+        <v>2.31</v>
+      </c>
+      <c r="AD9">
         <v>1.53</v>
-      </c>
-      <c r="AB9">
-        <v>2.37</v>
-      </c>
-      <c r="AC9">
-        <v>2.3</v>
-      </c>
-      <c r="AD9">
-        <v>1.57</v>
       </c>
       <c r="AE9">
         <v>1.2</v>
       </c>
       <c r="AF9">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AG9">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK9">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="Q2">
-        <v>3.25</v>
+        <v>2.53</v>
       </c>
       <c r="R2">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="S2">
+        <v>1.33</v>
+      </c>
+      <c r="T2">
+        <v>3.1</v>
+      </c>
+      <c r="U2">
+        <v>2.59</v>
+      </c>
+      <c r="V2">
+        <v>1.44</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>1.25</v>
+      </c>
+      <c r="Z2">
+        <v>3.65</v>
+      </c>
+      <c r="AA2">
+        <v>1.9</v>
+      </c>
+      <c r="AB2">
+        <v>2</v>
+      </c>
+      <c r="AC2">
+        <v>3.09</v>
+      </c>
+      <c r="AD2">
         <v>1.36</v>
       </c>
-      <c r="T2">
-        <v>2.75</v>
-      </c>
-      <c r="U2">
-        <v>2.64</v>
-      </c>
-      <c r="V2">
-        <v>1.43</v>
-      </c>
-      <c r="W2">
-        <v>1.08</v>
-      </c>
-      <c r="X2">
-        <v>1.05</v>
-      </c>
-      <c r="Y2">
-        <v>1.3</v>
-      </c>
-      <c r="Z2">
-        <v>3.38</v>
-      </c>
-      <c r="AA2">
-        <v>1.95</v>
-      </c>
-      <c r="AB2">
-        <v>1.73</v>
-      </c>
-      <c r="AC2">
-        <v>3.4</v>
-      </c>
-      <c r="AD2">
-        <v>1.3</v>
-      </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="O3">
+        <v>3.2</v>
+      </c>
+      <c r="P3">
+        <v>2.5</v>
+      </c>
+      <c r="Q3">
+        <v>3.25</v>
+      </c>
+      <c r="R3">
+        <v>2.01</v>
+      </c>
+      <c r="S3">
+        <v>1.36</v>
+      </c>
+      <c r="T3">
+        <v>2.75</v>
+      </c>
+      <c r="U3">
+        <v>2.64</v>
+      </c>
+      <c r="V3">
+        <v>1.43</v>
+      </c>
+      <c r="W3">
+        <v>1.08</v>
+      </c>
+      <c r="X3">
+        <v>1.05</v>
+      </c>
+      <c r="Y3">
+        <v>1.3</v>
+      </c>
+      <c r="Z3">
+        <v>3.38</v>
+      </c>
+      <c r="AA3">
+        <v>1.95</v>
+      </c>
+      <c r="AB3">
+        <v>1.73</v>
+      </c>
+      <c r="AC3">
         <v>3.4</v>
       </c>
-      <c r="P3">
-        <v>3.15</v>
-      </c>
-      <c r="Q3">
-        <v>2.53</v>
-      </c>
-      <c r="R3">
-        <v>2.18</v>
-      </c>
-      <c r="S3">
-        <v>1.33</v>
-      </c>
-      <c r="T3">
-        <v>3.1</v>
-      </c>
-      <c r="U3">
-        <v>2.59</v>
-      </c>
-      <c r="V3">
-        <v>1.44</v>
-      </c>
-      <c r="W3">
-        <v>1.07</v>
-      </c>
-      <c r="X3">
-        <v>1</v>
-      </c>
-      <c r="Y3">
-        <v>1.25</v>
-      </c>
-      <c r="Z3">
-        <v>3.65</v>
-      </c>
-      <c r="AA3">
-        <v>1.9</v>
-      </c>
-      <c r="AB3">
+      <c r="AD3">
+        <v>1.3</v>
+      </c>
+      <c r="AE3">
+        <v>1.1</v>
+      </c>
+      <c r="AF3">
+        <v>1.73</v>
+      </c>
+      <c r="AG3">
         <v>2</v>
-      </c>
-      <c r="AC3">
-        <v>3.09</v>
-      </c>
-      <c r="AD3">
-        <v>1.36</v>
-      </c>
-      <c r="AE3">
-        <v>1.09</v>
-      </c>
-      <c r="AF3">
-        <v>1.67</v>
-      </c>
-      <c r="AG3">
-        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O2">
+        <v>3.45</v>
+      </c>
+      <c r="P2">
+        <v>3.45</v>
+      </c>
+      <c r="Q2">
+        <v>2.57</v>
+      </c>
+      <c r="R2">
+        <v>2.04</v>
+      </c>
+      <c r="S2">
+        <v>1.36</v>
+      </c>
+      <c r="T2">
+        <v>3</v>
+      </c>
+      <c r="U2">
+        <v>2.63</v>
+      </c>
+      <c r="V2">
+        <v>1.43</v>
+      </c>
+      <c r="W2">
+        <v>1.05</v>
+      </c>
+      <c r="X2">
+        <v>1.02</v>
+      </c>
+      <c r="Y2">
+        <v>1.3</v>
+      </c>
+      <c r="Z2">
+        <v>3.77</v>
+      </c>
+      <c r="AA2">
+        <v>1.98</v>
+      </c>
+      <c r="AB2">
+        <v>1.82</v>
+      </c>
+      <c r="AC2">
         <v>3.4</v>
       </c>
-      <c r="P2">
-        <v>3.15</v>
-      </c>
-      <c r="Q2">
-        <v>2.53</v>
-      </c>
-      <c r="R2">
-        <v>2.18</v>
-      </c>
-      <c r="S2">
-        <v>1.33</v>
-      </c>
-      <c r="T2">
-        <v>3.1</v>
-      </c>
-      <c r="U2">
-        <v>2.59</v>
-      </c>
-      <c r="V2">
-        <v>1.44</v>
-      </c>
-      <c r="W2">
-        <v>1.07</v>
-      </c>
-      <c r="X2">
-        <v>1</v>
-      </c>
-      <c r="Y2">
-        <v>1.25</v>
-      </c>
-      <c r="Z2">
-        <v>3.65</v>
-      </c>
-      <c r="AA2">
-        <v>1.9</v>
-      </c>
-      <c r="AB2">
-        <v>2</v>
-      </c>
-      <c r="AC2">
-        <v>3.09</v>
-      </c>
       <c r="AD2">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P3">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q3">
         <v>3.25</v>
       </c>
       <c r="R3">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AA3">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB3">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
+        <v>1.28</v>
+      </c>
+      <c r="AK3">
         <v>1.33</v>
-      </c>
-      <c r="AK3">
-        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O4">
-        <v>3.51</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Q4">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="R4">
         <v>2.3</v>
       </c>
       <c r="S4">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="U4">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
         <v>4</v>
       </c>
       <c r="AA4">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC4">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="AD4">
         <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG4">
+        <v>1.92</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>2.15</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>2.02</v>
-      </c>
       <c r="AK4">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="O5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q5">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U5">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
         <v>1.38</v>
       </c>
       <c r="Z5">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AA5">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AB5">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC5">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
         <v>2.1</v>
       </c>
       <c r="AG5">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK5">
         <v>2.22</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="O6">
         <v>4.2</v>
       </c>
       <c r="P6">
-        <v>6.25</v>
+        <v>5.43</v>
       </c>
       <c r="Q6">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
         <v>3.16</v>
       </c>
       <c r="U6">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC6">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AD6">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,80 +1450,80 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="P7">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="Q7">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="R7">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="V7">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z7">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA7">
+        <v>1.58</v>
+      </c>
+      <c r="AB7">
+        <v>2.39</v>
+      </c>
+      <c r="AC7">
+        <v>2.88</v>
+      </c>
+      <c r="AD7">
+        <v>1.42</v>
+      </c>
+      <c r="AE7">
+        <v>1.15</v>
+      </c>
+      <c r="AF7">
+        <v>1.62</v>
+      </c>
+      <c r="AG7">
+        <v>2.15</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
+        <v>1.38</v>
+      </c>
+      <c r="AK7">
         <v>1.6</v>
-      </c>
-      <c r="AB7">
-        <v>2.3</v>
-      </c>
-      <c r="AC7">
-        <v>2.35</v>
-      </c>
-      <c r="AD7">
-        <v>1.51</v>
-      </c>
-      <c r="AE7">
-        <v>1.2</v>
-      </c>
-      <c r="AF7">
-        <v>1.48</v>
-      </c>
-      <c r="AG7">
-        <v>2.4</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.44</v>
-      </c>
-      <c r="AK7">
-        <v>1.62</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q8">
-        <v>3.88</v>
+        <v>3.54</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8">
         <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
       <c r="AA8">
         <v>1.71</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC8">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG8">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK8">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
         <v>8</v>
       </c>
       <c r="P9">
-        <v>14.78</v>
+        <v>16</v>
       </c>
       <c r="Q9">
         <v>1.5</v>
       </c>
       <c r="R9">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="S9">
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="U9">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V9">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W9">
         <v>1.14</v>
@@ -1812,28 +1812,28 @@
         <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AA9">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB9">
         <v>2.4</v>
       </c>
       <c r="AC9">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AD9">
         <v>1.53</v>
       </c>
       <c r="AE9">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF9">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AG9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK9">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q10">
         <v>3.9</v>
@@ -1954,49 +1954,49 @@
         <v>2.75</v>
       </c>
       <c r="S10">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T10">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="U10">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="V10">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W10">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z10">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA10">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB10">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AC10">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AD10">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AE10">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF10">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AG10">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="P11">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="S11">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T11">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="U11">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V11">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W11">
         <v>1.22</v>
@@ -2135,31 +2135,31 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>6.85</v>
       </c>
       <c r="AA11">
+        <v>1.36</v>
+      </c>
+      <c r="AB11">
+        <v>3.1</v>
+      </c>
+      <c r="AC11">
+        <v>1.82</v>
+      </c>
+      <c r="AD11">
+        <v>1.85</v>
+      </c>
+      <c r="AE11">
+        <v>1.34</v>
+      </c>
+      <c r="AF11">
         <v>1.3</v>
       </c>
-      <c r="AB11">
-        <v>3.08</v>
-      </c>
-      <c r="AC11">
-        <v>1.83</v>
-      </c>
-      <c r="AD11">
-        <v>1.93</v>
-      </c>
-      <c r="AE11">
-        <v>1.33</v>
-      </c>
-      <c r="AF11">
-        <v>1.32</v>
-      </c>
       <c r="AG11">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK11">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="O12">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="S12">
         <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U12">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA12">
+        <v>1.52</v>
+      </c>
+      <c r="AB12">
+        <v>2.24</v>
+      </c>
+      <c r="AC12">
+        <v>2.34</v>
+      </c>
+      <c r="AD12">
         <v>1.5</v>
       </c>
-      <c r="AB12">
-        <v>2.39</v>
-      </c>
-      <c r="AC12">
-        <v>2.22</v>
-      </c>
-      <c r="AD12">
-        <v>1.58</v>
-      </c>
       <c r="AE12">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
         <v>1.44</v>
       </c>
       <c r="AG12">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK12">
         <v>1.4</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O13">
         <v>5.1</v>
       </c>
       <c r="P13">
-        <v>7.65</v>
+        <v>6.1</v>
       </c>
       <c r="Q13">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="R13">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="S13">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="V13">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Z13">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA13">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AC13">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AD13">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AE13">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AF13">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG13">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.1</v>
       </c>
       <c r="AK13">
-        <v>3.02</v>
+        <v>2.5</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-08-04.xlsx
+++ b/jogos_2026-08-04.xlsx
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -624,14 +624,14 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78", "90+4"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "70"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1113,14 +1113,14 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "45+4", "88"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "29", "90+1"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1581,139 +1581,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>1.95</v>
+        <v>16</v>
       </c>
       <c r="Q8">
-        <v>3.54</v>
+        <v>1.5</v>
       </c>
       <c r="R8">
-        <v>2.18</v>
+        <v>3.1</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="U8">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA8">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AB8">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="AC8">
-        <v>2.79</v>
+        <v>2.45</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF8">
-        <v>1.58</v>
+        <v>2.58</v>
       </c>
       <c r="AG8">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
+          <t>["31", "33", "51", "76", "90+4"]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ8">
-        <v>1.73</v>
+        <v>1.06</v>
       </c>
       <c r="AK8">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1744,139 +1744,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="P9">
-        <v>16</v>
+        <v>1.95</v>
       </c>
       <c r="Q9">
+        <v>3.54</v>
+      </c>
+      <c r="R9">
+        <v>2.18</v>
+      </c>
+      <c r="S9">
+        <v>1.33</v>
+      </c>
+      <c r="T9">
+        <v>3.1</v>
+      </c>
+      <c r="U9">
+        <v>2.54</v>
+      </c>
+      <c r="V9">
         <v>1.5</v>
       </c>
-      <c r="R9">
-        <v>3.1</v>
-      </c>
-      <c r="S9">
-        <v>1.25</v>
-      </c>
-      <c r="T9">
-        <v>3.14</v>
-      </c>
-      <c r="U9">
-        <v>2.25</v>
-      </c>
-      <c r="V9">
-        <v>1.6</v>
-      </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA9">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="AC9">
-        <v>2.45</v>
+        <v>2.79</v>
       </c>
       <c r="AD9">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
+        <v>1.13</v>
+      </c>
+      <c r="AF9">
+        <v>1.58</v>
+      </c>
+      <c r="AG9">
+        <v>2.2</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>["63", "69"]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>["45"]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.73</v>
+      </c>
+      <c r="AK9">
+        <v>1.25</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>3</v>
+      </c>
+      <c r="AN9">
+        <v>4</v>
+      </c>
+      <c r="AO9">
+        <v>9</v>
+      </c>
+      <c r="AP9">
+        <v>11</v>
+      </c>
+      <c r="AQ9">
         <v>1.16</v>
       </c>
-      <c r="AF9">
-        <v>2.58</v>
-      </c>
-      <c r="AG9">
-        <v>1.44</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.06</v>
-      </c>
-      <c r="AK9">
-        <v>5</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-1</v>
-      </c>
-      <c r="AN9">
-        <v>-1</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>-1</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
